--- a/tame_output/ON/bt/strategyON_20240604.xlsx
+++ b/tame_output/ON/bt/strategyON_20240604.xlsx
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913421</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.753744406747933</v>
+        <v>3.753744406747937</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.142046681530043</v>
+        <v>-5.141954408367591</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7671612244566806</v>
+        <v>0.7671981337216613</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5778898150148081</v>
+        <v>-0.5781610550399325</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.477602432373561</v>
+        <v>2.477439688358486</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240604.xlsx
+++ b/tame_output/ON/bt/strategyON_20240604.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,17 +987,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>454.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-675.8%</t>
+          <t>-667.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-36.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-162.5%</t>
+          <t>188.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-299.5%</t>
+          <t>-296.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-281.8%</t>
+          <t>-273.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-198.3%</t>
+          <t>-193.5%</t>
         </is>
       </c>
     </row>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.908366367491769</v>
+        <v>-7.81974511257817</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07618665652536016</v>
+        <v>-0.04073815455992058</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.713076263838035</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>2.059670556482274</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.76042632608417</v>
+        <v>-7.671805071170571</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.136889562650488</v>
+        <v>-0.1014410606850484</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.692755347929478</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.951984183339241</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.743268175952876</v>
+        <v>-7.654646921039276</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1387402888514488</v>
+        <v>-0.1032917868860088</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.675597197798183</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.953565087164539</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.699719769182185</v>
+        <v>-7.611098514268586</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1282815382382658</v>
+        <v>-0.0928330362728258</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.675597197798183</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.946604475069446</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.457571375728327</v>
+        <v>-7.368950120814728</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01695982647557948</v>
+        <v>0.01848867548986055</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.675597197798183</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.961066829450589</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.349312238605806</v>
+        <v>-7.260690983692206</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.02087594883262422</v>
+        <v>0.05632445079806425</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.675597197798183</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.955598949909784</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.226021103788675</v>
+        <v>-7.137399848875075</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06769049677005379</v>
+        <v>0.1031389987354934</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.552306062981053</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>2.02707172481064</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.204871904885231</v>
+        <v>-7.116250649971632</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08385115456875614</v>
+        <v>0.1192996565341957</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.531156864077609</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>2.047462222390031</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.961106462901787</v>
+        <v>-6.872485207988188</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1771380397091846</v>
+        <v>0.2125865416746242</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.531156864077609</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>2.043242930737081</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.859343642624492</v>
+        <v>-6.770722387710893</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2199674817401185</v>
+        <v>0.2554159837055581</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.517937795685181</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>2.053298685692555</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.609493248675418</v>
+        <v>-6.520871993761818</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3126497143034506</v>
+        <v>0.3480982162688901</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.517937795685181</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>2.046040760676257</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.433601156207985</v>
+        <v>-6.344979901294385</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3866056748110722</v>
+        <v>0.4220541767765122</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.517937795685181</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>2.049639884196906</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.262154693185521</v>
+        <v>-6.173533438271922</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4685117660746116</v>
+        <v>0.5039602680400512</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.346491332662717</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.165835268064937</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.037121693516698</v>
+        <v>-5.948500438603099</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5575454435584377</v>
+        <v>0.5929939455238773</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.121458332993895</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.299875545482528</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.973485951282764</v>
+        <v>-5.884864696369164</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5876945415063286</v>
+        <v>0.6231430434717686</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.05782259075996</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.342751791877206</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.880485910076866</v>
+        <v>-5.791864655163266</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6060888167724836</v>
+        <v>0.6415373187379236</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.05782259075996</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.323946050661001</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.640055413272005</v>
+        <v>-5.551434158358406</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7040040921193054</v>
+        <v>0.739452594084745</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.8173920939550998</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.469947425368795</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.567812845100811</v>
+        <v>-5.479191590187211</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7368304332226034</v>
+        <v>0.772278935188043</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.8173920939550998</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.473876739203615</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.514814522819423</v>
+        <v>-5.426193267905823</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7587083460524986</v>
+        <v>0.7941568480179382</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.762055834953161</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.507757078522118</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.406009637339696</v>
+        <v>-5.317388382426096</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7992283714643826</v>
+        <v>0.8346768734298227</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.762055834953161</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.504755149742112</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.185988839302685</v>
+        <v>-5.097367584389086</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.888815727689801</v>
+        <v>0.924264229655241</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.6208359898851807</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.591066093793514</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.053121150239408</v>
+        <v>-4.964499895325808</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9578569861169353</v>
+        <v>0.9933054880823753</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.6208359898851807</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.606960276595338</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.893606046720038</v>
+        <v>-4.804984791806438</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.022808871964985</v>
+        <v>1.058257373930425</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.4613208863658108</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.703815183147261</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.7489339016203</v>
+        <v>-4.660312646706701</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.09076583256632</v>
+        <v>1.12621433453176</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.3166487412660734</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.800706572768544</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.808808728977993</v>
+        <v>-4.720187474064393</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.052853393024669</v>
+        <v>1.088301894990109</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.3765235686237655</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.750819167755354</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.722009231198983</v>
+        <v>-4.633387976285384</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.109973685458839</v>
+        <v>1.145422187424278</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.3765235686237655</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.773219661077921</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.724478937660789</v>
+        <v>-4.63585768274719</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.109058204247529</v>
+        <v>1.144506706212968</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.3789932750855717</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.771810238574249</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.7928491239848</v>
+        <v>-4.7042278690712</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.092717052192626</v>
+        <v>1.128165554158066</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3697175760493567</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.78838258047068</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.901387304900934</v>
+        <v>-4.812766049987334</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.039738488458064</v>
+        <v>1.075186990423504</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3697175760493567</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.778819289102571</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.932380464229639</v>
+        <v>-4.84375920931604</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8520507897669689</v>
+        <v>0.8874992917324085</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3697175760493567</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.603528854142958</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.75690620443717</v>
+        <v>-4.668284949523571</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9268077256757441</v>
+        <v>0.9622562276411839</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3697175760493567</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.608096086134746</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.867842457078419</v>
+        <v>-4.77922120216482</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8581752533804516</v>
+        <v>0.8936237553458914</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3697175760493567</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.583838114895953</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.070869034621652</v>
+        <v>-4.982247779708053</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7800960075830639</v>
+        <v>0.8155445095485037</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5727441535925901</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.465153553589918</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.912943435686359</v>
+        <v>-4.82432218077276</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8534386335893134</v>
+        <v>0.8888871355547532</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5727441535925901</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.475325940022051</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.826699972659982</v>
+        <v>-4.738078717746382</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8828822893737249</v>
+        <v>0.9183307913391645</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5727441535925901</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.470272210595911</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.872006792058961</v>
+        <v>-4.783385537145362</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8565353370586584</v>
+        <v>0.8919838390240982</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6135543166018209</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.437561888234898</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.901039896761263</v>
+        <v>-4.812418641847663</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8454739682108396</v>
+        <v>0.8809224701762792</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6135543166018209</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.438113761268</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.808229415310403</v>
+        <v>-4.719608160396803</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8118708526825491</v>
+        <v>0.8473193546479889</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.5207438351509616</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.423072742029881</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.85261888463983</v>
+        <v>-4.763997629726231</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7959885408753788</v>
+        <v>0.8314370428408187</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.5651333044803892</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.398312536356825</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.73994766640358</v>
+        <v>-4.651326411489981</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.836132736681602</v>
+        <v>0.8715812386470416</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.452462086244139</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.460990975810298</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.627570665220907</v>
+        <v>-4.538949410307308</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8865748329853385</v>
+        <v>0.922023334950778</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.452462086244139</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.466482271640965</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.825805234107638</v>
+        <v>-4.737183979194039</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8187782071991851</v>
+        <v>0.854226709164625</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.6506966551308696</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.359038732077466</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.908806515132917</v>
+        <v>-4.820185260219318</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6239334147897269</v>
+        <v>0.6593819167551667</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.6692675396580434</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.136491917560329</v>
+        <v>2.186251921361815</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.035873521439905</v>
+        <v>-4.947252266526306</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6932562729861371</v>
+        <v>0.7287047749515769</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.6692675396580434</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.256641578279534</v>
+        <v>2.306401582081021</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.122472104421008</v>
+        <v>-5.033850849507409</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6731298658960192</v>
+        <v>0.7085783678614588</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.6692675396580434</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.271154604381857</v>
+        <v>2.320914608183344</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.084088441862857</v>
+        <v>-4.995467186949258</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.685902772261648</v>
+        <v>0.721351274227088</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.6308838770998922</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.291604243259116</v>
+        <v>2.341364247060603</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.906972111827691</v>
+        <v>-4.818350856914091</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7534783331210164</v>
+        <v>0.7889268350864562</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.6308838770998922</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.288333272104418</v>
+        <v>2.338093275905905</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.877269987851397</v>
+        <v>-4.788648732937798</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7660425744734471</v>
+        <v>0.8014910764388867</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7182873419843501</v>
+        <v>-0.6353540023152056</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.286334588737144</v>
+        <v>2.33609459253863</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.697894566612629</v>
+        <v>-4.60927331169903</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8315797182753686</v>
+        <v>0.8670282202408082</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5615105838136314</v>
+        <v>-0.4785772441444869</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.374187618945989</v>
+        <v>2.423947622747476</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.742908780133236</v>
+        <v>-4.654287525219637</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7943814881987157</v>
+        <v>0.8298299901641553</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.591859479128236</v>
+        <v>-0.5089261394590915</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.336785737088816</v>
+        <v>2.386545740890303</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.009913290405671</v>
+        <v>-4.921292035492072</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6932712464286874</v>
+        <v>0.728719748394127</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7862225171711845</v>
+        <v>-0.70328917750204</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.225859476601993</v>
+        <v>2.275619480403479</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.111111071842844</v>
+        <v>-5.022489816929244</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6519960557503195</v>
+        <v>0.6874445577157595</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.7716979910473591</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.184018110371303</v>
+        <v>2.233778114172789</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.078635485672072</v>
+        <v>-4.990014230758472</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6625862517729453</v>
+        <v>0.6980347537383851</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.7716979910473591</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.18161807192562</v>
+        <v>2.231378075727106</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.059597357964774</v>
+        <v>-4.970976103051175</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.666726222064109</v>
+        <v>0.7021747240295488</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.8298816023785537</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.143232624335147</v>
+        <v>2.192992628136635</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.090723989115393</v>
+        <v>-5.002102734201793</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8318574385425421</v>
+        <v>0.8673059405079822</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.8298816023785537</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.320814493273828</v>
+        <v>2.370574497075315</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.143044369716185</v>
+        <v>-5.054423114802585</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8117626152883592</v>
+        <v>0.8472111172537988</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.7949347423696815</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.342615938265285</v>
+        <v>2.392375942066772</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.287367275641103</v>
+        <v>-5.198746020727504</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7600419833153174</v>
+        <v>0.7954904852807574</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.7949347423696815</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.348624468662211</v>
+        <v>2.398384472463698</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.139624305406101</v>
+        <v>-5.051003050492501</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8982918192013405</v>
+        <v>0.9337403211667801</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.6271273851347984</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.528461530795163</v>
+        <v>2.57822153459665</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.241638987937322</v>
+        <v>-5.153017733023723</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8602795677203328</v>
+        <v>0.8957280696857728</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.6271273851347984</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.531255152326644</v>
+        <v>2.581015156128131</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.105029643843229</v>
+        <v>-5.01640838892963</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9155856537496283</v>
+        <v>0.9510341557150683</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5734513807098505</v>
+        <v>-0.4905180410407059</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.613883107174757</v>
+        <v>2.663643110976244</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.24779497666588</v>
+        <v>-5.15917372175228</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8575599973606787</v>
+        <v>0.8930084993261183</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.6332833738633563</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.527304384221277</v>
+        <v>2.577064388022764</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.185496977889757</v>
+        <v>-5.096875722976158</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9488147506679483</v>
+        <v>0.9842632526333883</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.6332833738633563</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.593639938018098</v>
+        <v>2.643399941819585</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.983706780224599</v>
+        <v>-4.895085525311</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7381117021234096</v>
+        <v>0.7735602040888494</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5181985213633464</v>
+        <v>-0.4352651816942019</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.421031725708989</v>
+        <v>2.470791729510476</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.923816098582006</v>
+        <v>-4.835194843668407</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8323582071026221</v>
+        <v>0.8678067090680619</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.458307839720753</v>
+        <v>-0.3753745000516084</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.527256367016721</v>
+        <v>2.577016370818207</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.02155664320698</v>
+        <v>-4.932935388293381</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8078897253686761</v>
+        <v>0.8433382273341157</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4741971178537331</v>
+        <v>-0.3912637781845886</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.532350536252976</v>
+        <v>2.582110540054463</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.19789440332991</v>
+        <v>-5.10927314841631</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7358906021441758</v>
+        <v>0.7713391041096158</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.567601538307518</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.42508386100389</v>
+        <v>2.474843864805377</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.197205031168687</v>
+        <v>-5.108583776255087</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7346579690485937</v>
+        <v>0.7701064710140337</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.567601538307518</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.423575479043818</v>
+        <v>2.473335482845305</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.203775996223279</v>
+        <v>-5.11515474130968</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7318924504621931</v>
+        <v>0.7673409524276327</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.574172503362111</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.419495767446499</v>
+        <v>2.469255771247986</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.195822025928507</v>
+        <v>-5.107200771014908</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7350740385801018</v>
+        <v>0.7705225405455414</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.574172503362111</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.419495767446499</v>
+        <v>2.469255771247986</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.18544864959542</v>
+        <v>-5.096827394681821</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7456051461411413</v>
+        <v>0.7810536481065808</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6467324666981682</v>
+        <v>-0.5637991270290237</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.432101550274156</v>
+        <v>2.481861554075643</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.057764339801124</v>
+        <v>-4.969143084887524</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8015712434335844</v>
+        <v>0.8370197453990242</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5190481569038717</v>
+        <v>-0.4361148172347272</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.513604509525459</v>
+        <v>2.563364513326945</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.118430930203512</v>
+        <v>-5.029809675289913</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7640592797485013</v>
+        <v>0.7995077817139409</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6007464736224054</v>
+        <v>-0.5178131339532609</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.451340191970211</v>
+        <v>2.501100195771698</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.053437070269867</v>
+        <v>-4.964815815356268</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.794154526332588</v>
+        <v>0.8296030282980278</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.57391585901825</v>
+        <v>-0.4909825193491055</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.471536263343332</v>
+        <v>2.521296267144819</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.154195706026865</v>
+        <v>-5.065574451113266</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7580120116608668</v>
+        <v>0.7934605136263064</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6627414277452555</v>
+        <v>-0.579808088076111</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.422401861738207</v>
+        <v>2.472161865539694</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.109992868940965</v>
+        <v>-5.021371614027365</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7815727490230642</v>
+        <v>0.8170212509885038</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.618538590659355</v>
+        <v>-0.5356052509902105</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.454803166517585</v>
+        <v>2.504563170319071</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.753744406747937</v>
+        <v>3.844252838692812</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.141954408367591</v>
+        <v>-5.058350641690808</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7671981337216613</v>
+        <v>0.8006396403923746</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5781610550399325</v>
+        <v>-0.49863134919888</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.477439688358486</v>
+        <v>2.525157511863117</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240604.xlsx
+++ b/tame_output/ON/bt/strategyON_20240604.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>44.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.3%</t>
+          <t>452.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-667.4%</t>
+          <t>-676.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>188.6%</t>
+          <t>-162.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-296.2%</t>
+          <t>-299.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.2%</t>
+          <t>-154.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.9%</t>
+          <t>-288.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-193.5%</t>
+          <t>-202.5%</t>
         </is>
       </c>
     </row>
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.81974511257817</v>
+        <v>-7.908366367491769</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.04073815455992058</v>
+        <v>-0.07618665652536016</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.713076263838035</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.059670556482274</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.671805071170571</v>
+        <v>-7.76042632608417</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1014410606850484</v>
+        <v>-0.136889562650488</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.692755347929478</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.951984183339241</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.654646921039276</v>
+        <v>-7.743268175952876</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1032917868860088</v>
+        <v>-0.1387402888514488</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.675597197798183</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.953565087164539</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.611098514268586</v>
+        <v>-7.699719769182185</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.0928330362728258</v>
+        <v>-0.1282815382382658</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.675597197798183</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.946604475069446</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.368950120814728</v>
+        <v>-7.457571375728327</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.01848867548986055</v>
+        <v>-0.01695982647557948</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.675597197798183</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.961066829450589</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.260690983692206</v>
+        <v>-7.349312238605806</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05632445079806425</v>
+        <v>0.02087594883262422</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.675597197798183</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.955598949909784</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.137399848875075</v>
+        <v>-7.226021103788675</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1031389987354934</v>
+        <v>0.06769049677005379</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.552306062981053</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.02707172481064</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.116250649971632</v>
+        <v>-7.204871904885231</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1192996565341957</v>
+        <v>0.08385115456875614</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.531156864077609</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.047462222390031</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.872485207988188</v>
+        <v>-6.961106462901787</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2125865416746242</v>
+        <v>0.1771380397091846</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.531156864077609</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.043242930737081</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.770722387710893</v>
+        <v>-6.859343642624492</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2554159837055581</v>
+        <v>0.2199674817401185</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.517937795685181</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.053298685692555</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.520871993761818</v>
+        <v>-6.609493248675418</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3480982162688901</v>
+        <v>0.3126497143034506</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.517937795685181</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.046040760676257</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.344979901294385</v>
+        <v>-6.433601156207985</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4220541767765122</v>
+        <v>0.3866056748110722</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.517937795685181</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.049639884196906</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.173533438271922</v>
+        <v>-6.262154693185521</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5039602680400512</v>
+        <v>0.4685117660746116</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.346491332662717</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.165835268064937</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.948500438603099</v>
+        <v>-6.037121693516698</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5929939455238773</v>
+        <v>0.5575454435584377</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.121458332993895</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.299875545482528</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.884864696369164</v>
+        <v>-5.973485951282764</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6231430434717686</v>
+        <v>0.5876945415063286</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.05782259075996</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.342751791877206</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.791864655163266</v>
+        <v>-5.880485910076866</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6415373187379236</v>
+        <v>0.6060888167724836</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.05782259075996</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.323946050661001</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.551434158358406</v>
+        <v>-5.640055413272005</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.739452594084745</v>
+        <v>0.7040040921193054</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8173920939550998</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.469947425368795</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.479191590187211</v>
+        <v>-5.567812845100811</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.772278935188043</v>
+        <v>0.7368304332226034</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8173920939550998</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.473876739203615</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.426193267905823</v>
+        <v>-5.514814522819423</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7941568480179382</v>
+        <v>0.7587083460524986</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.762055834953161</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.507757078522118</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.317388382426096</v>
+        <v>-5.406009637339696</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8346768734298227</v>
+        <v>0.7992283714643826</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.762055834953161</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.504755149742112</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.097367584389086</v>
+        <v>-5.185988839302685</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.924264229655241</v>
+        <v>0.888815727689801</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6208359898851807</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.591066093793514</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.964499895325808</v>
+        <v>-5.053121150239408</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9933054880823753</v>
+        <v>0.9578569861169353</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6208359898851807</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.606960276595338</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.804984791806438</v>
+        <v>-4.893606046720038</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.058257373930425</v>
+        <v>1.022808871964985</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4613208863658108</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.703815183147261</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.660312646706701</v>
+        <v>-4.7489339016203</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.12621433453176</v>
+        <v>1.09076583256632</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3166487412660734</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.800706572768544</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.720187474064393</v>
+        <v>-4.808808728977993</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.088301894990109</v>
+        <v>1.052853393024669</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3765235686237655</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.750819167755354</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.633387976285384</v>
+        <v>-4.722009231198983</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.145422187424278</v>
+        <v>1.109973685458839</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3765235686237655</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.773219661077921</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.63585768274719</v>
+        <v>-4.724478937660789</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.144506706212968</v>
+        <v>1.109058204247529</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3789932750855717</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.771810238574249</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.7042278690712</v>
+        <v>-4.7928491239848</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.128165554158066</v>
+        <v>1.092717052192626</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3697175760493567</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.78838258047068</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.812766049987334</v>
+        <v>-4.901387304900934</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.075186990423504</v>
+        <v>1.039738488458064</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3697175760493567</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.778819289102571</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.84375920931604</v>
+        <v>-4.932380464229639</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8874992917324085</v>
+        <v>0.8520507897669689</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3697175760493567</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.603528854142958</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.668284949523571</v>
+        <v>-4.75690620443717</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9622562276411839</v>
+        <v>0.9268077256757441</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3697175760493567</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.608096086134746</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.77922120216482</v>
+        <v>-4.867842457078419</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8936237553458914</v>
+        <v>0.8581752533804516</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3697175760493567</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.583838114895953</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.982247779708053</v>
+        <v>-5.070869034621652</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8155445095485037</v>
+        <v>0.7800960075830639</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5727441535925901</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.465153553589918</v>
+        <v>2.415393549788432</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.82432218077276</v>
+        <v>-4.912943435686359</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8888871355547532</v>
+        <v>0.8534386335893134</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5727441535925901</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.475325940022051</v>
+        <v>2.425565936220564</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.738078717746382</v>
+        <v>-4.826699972659982</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9183307913391645</v>
+        <v>0.8828822893737249</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5727441535925901</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.470272210595911</v>
+        <v>2.420512206794424</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.783385537145362</v>
+        <v>-4.872006792058961</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8919838390240982</v>
+        <v>0.8565353370586584</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6135543166018209</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.437561888234898</v>
+        <v>2.387801884433411</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.812418641847663</v>
+        <v>-4.901039896761263</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8809224701762792</v>
+        <v>0.8454739682108396</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6135543166018209</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.438113761268</v>
+        <v>2.388353757466513</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.719608160396803</v>
+        <v>-4.808229415310403</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8473193546479889</v>
+        <v>0.8118708526825491</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5207438351509616</v>
+        <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.423072742029881</v>
+        <v>2.373312738228394</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.763997629726231</v>
+        <v>-4.85261888463983</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8314370428408187</v>
+        <v>0.7959885408753788</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5651333044803892</v>
+        <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.398312536356825</v>
+        <v>2.348552532555338</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.651326411489981</v>
+        <v>-4.73994766640358</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8715812386470416</v>
+        <v>0.836132736681602</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.452462086244139</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.460990975810298</v>
+        <v>2.411230972008811</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.538949410307308</v>
+        <v>-4.627570665220907</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.922023334950778</v>
+        <v>0.8865748329853385</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.452462086244139</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.466482271640965</v>
+        <v>2.416722267839479</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.737183979194039</v>
+        <v>-4.825805234107638</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.854226709164625</v>
+        <v>0.8187782071991851</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6506966551308696</v>
+        <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.359038732077466</v>
+        <v>2.309278728275979</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.820185260219318</v>
+        <v>-4.910620947726552</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6593819167551667</v>
+        <v>0.6232076417522727</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6692675396580434</v>
+        <v>-0.8197635214746963</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.186251921361815</v>
+        <v>2.095954332271823</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.947252266526306</v>
+        <v>-5.03768795403354</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7287047749515769</v>
+        <v>0.692530499948683</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6692675396580434</v>
+        <v>-0.8197635214746963</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.306401582081021</v>
+        <v>2.216103992991029</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.033850849507409</v>
+        <v>-5.124286537014643</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7085783678614588</v>
+        <v>0.6724040928585651</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6692675396580434</v>
+        <v>-0.8197635214746963</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.320914608183344</v>
+        <v>2.230617019093352</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.995467186949258</v>
+        <v>-5.085902874456492</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.721351274227088</v>
+        <v>0.6851769992241943</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.6308838770998922</v>
+        <v>-0.7813798589165452</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.341364247060603</v>
+        <v>2.251066657970612</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.818350856914091</v>
+        <v>-4.908786544421326</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7889268350864562</v>
+        <v>0.7527525600835625</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.6308838770998922</v>
+        <v>-0.7813798589165452</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.338093275905905</v>
+        <v>2.247795686815913</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.788648732937798</v>
+        <v>-4.879084420445032</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8014910764388867</v>
+        <v>0.765316801435993</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.6353540023152056</v>
+        <v>-0.7858499841318585</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.33609459253863</v>
+        <v>2.245797003448638</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.60927331169903</v>
+        <v>-4.699708999206265</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8670282202408082</v>
+        <v>0.8308539452379144</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4785772441444869</v>
+        <v>-0.6290732259611398</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.423947622747476</v>
+        <v>2.333650033657484</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.654287525219637</v>
+        <v>-4.744723212726871</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8298299901641553</v>
+        <v>0.7936557151612615</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.5089261394590915</v>
+        <v>-0.6594221212757444</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.386545740890303</v>
+        <v>2.296248151800311</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.921292035492072</v>
+        <v>-5.011727722999306</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.728719748394127</v>
+        <v>0.6925454733912333</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.70328917750204</v>
+        <v>-0.8537851593186929</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.275619480403479</v>
+        <v>2.185321891313488</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.022489816929244</v>
+        <v>-5.112925504436479</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6874445577157595</v>
+        <v>0.6512702827128658</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7716979910473591</v>
+        <v>-0.9221939728640121</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.233778114172789</v>
+        <v>2.143480525082798</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.990014230758472</v>
+        <v>-5.080449918265707</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6980347537383851</v>
+        <v>0.6618604787354911</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7716979910473591</v>
+        <v>-0.9221939728640121</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.231378075727106</v>
+        <v>2.141080486637114</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.970976103051175</v>
+        <v>-5.06141179055841</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7021747240295488</v>
+        <v>0.6660004490266549</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.8298816023785537</v>
+        <v>-0.9803775841952066</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.192992628136635</v>
+        <v>2.102695039046643</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.002102734201793</v>
+        <v>-5.092538421709028</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8673059405079822</v>
+        <v>0.8311316655050884</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.8298816023785537</v>
+        <v>-0.9803775841952066</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.370574497075315</v>
+        <v>2.280276907985323</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.054423114802585</v>
+        <v>-5.14485880230982</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8472111172537988</v>
+        <v>0.8110368422509051</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7949347423696815</v>
+        <v>-0.9454307241863344</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.392375942066772</v>
+        <v>2.30207835297678</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.198746020727504</v>
+        <v>-5.289181708234739</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7954904852807574</v>
+        <v>0.7593162102778637</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7949347423696815</v>
+        <v>-0.9454307241863344</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.398384472463698</v>
+        <v>2.308086883373706</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.051003050492501</v>
+        <v>-5.141438737999736</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9337403211667801</v>
+        <v>0.8975660461638864</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.6271273851347984</v>
+        <v>-0.7776233669514513</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.57822153459665</v>
+        <v>2.487923945506658</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.153017733023723</v>
+        <v>-5.243453420530957</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8957280696857728</v>
+        <v>0.8595537946828791</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.6271273851347984</v>
+        <v>-0.7776233669514513</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.581015156128131</v>
+        <v>2.490717567038139</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.01640838892963</v>
+        <v>-5.106844076436865</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9510341557150683</v>
+        <v>0.9148598807121742</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4905180410407059</v>
+        <v>-0.6410140228573589</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.663643110976244</v>
+        <v>2.573345521886253</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.15917372175228</v>
+        <v>-5.249609409259515</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8930084993261183</v>
+        <v>0.8568342243232245</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6332833738633563</v>
+        <v>-0.7837793556800092</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.577064388022764</v>
+        <v>2.486766798932773</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.096875722976158</v>
+        <v>-5.187311410483392</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9842632526333883</v>
+        <v>0.9480889776304942</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6332833738633563</v>
+        <v>-0.7837793556800092</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.643399941819585</v>
+        <v>2.553102352729594</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.895085525311</v>
+        <v>-4.985521212818234</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7735602040888494</v>
+        <v>0.7373859290859555</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4352651816942019</v>
+        <v>-0.5857611635108548</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.470791729510476</v>
+        <v>2.380494140420484</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.835194843668407</v>
+        <v>-4.925630531175641</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8678067090680619</v>
+        <v>0.8316324340651682</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3753745000516084</v>
+        <v>-0.5258704818682614</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.577016370818207</v>
+        <v>2.486718781728215</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.932935388293381</v>
+        <v>-5.023371075800616</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8433382273341157</v>
+        <v>0.807163952331222</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3912637781845886</v>
+        <v>-0.5417597600012416</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.582110540054463</v>
+        <v>2.491812950964471</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.10927314841631</v>
+        <v>-5.199708835923545</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7713391041096158</v>
+        <v>0.7351648291067221</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.567601538307518</v>
+        <v>-0.7180975201241711</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.474843864805377</v>
+        <v>2.384546275715385</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.108583776255087</v>
+        <v>-5.199019463762322</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7701064710140337</v>
+        <v>0.7339321960111396</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.567601538307518</v>
+        <v>-0.7180975201241711</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.473335482845305</v>
+        <v>2.383037893755314</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.11515474130968</v>
+        <v>-5.205590428816914</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7673409524276327</v>
+        <v>0.731166677424739</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.574172503362111</v>
+        <v>-0.7246684851787639</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.469255771247986</v>
+        <v>2.378958182157994</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.107200771014908</v>
+        <v>-5.197636458522142</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7705225405455414</v>
+        <v>0.7343482655426476</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.574172503362111</v>
+        <v>-0.7246684851787639</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.469255771247986</v>
+        <v>2.378958182157994</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.096827394681821</v>
+        <v>-5.187263082189055</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7810536481065808</v>
+        <v>0.7448793731036871</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.5637991270290237</v>
+        <v>-0.7142951088456766</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.481861554075643</v>
+        <v>2.391563964985651</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.969143084887524</v>
+        <v>-5.059578772394759</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8370197453990242</v>
+        <v>0.8008454703961303</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4361148172347272</v>
+        <v>-0.5866107990513801</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.563364513326945</v>
+        <v>2.473066924236954</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.029809675289913</v>
+        <v>-5.120245362797148</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7995077817139409</v>
+        <v>0.7633335067110472</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.5178131339532609</v>
+        <v>-0.6683091157699138</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.501100195771698</v>
+        <v>2.410802606681706</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.964815815356268</v>
+        <v>-5.055251502863502</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8296030282980278</v>
+        <v>0.7934287532951338</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4909825193491055</v>
+        <v>-0.6414785011657584</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.521296267144819</v>
+        <v>2.430998678054828</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.065574451113266</v>
+        <v>-5.1560101386205</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7934605136263064</v>
+        <v>0.7572862386234127</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.579808088076111</v>
+        <v>-0.7303040698927639</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.472161865539694</v>
+        <v>2.381864276449702</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.021371614027365</v>
+        <v>-5.1118073015346</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8170212509885038</v>
+        <v>0.78084697598561</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5356052509902105</v>
+        <v>-0.6861012328068634</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.504563170319071</v>
+        <v>2.414265581229079</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.844252838692812</v>
+        <v>3.720666498268026</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.058350641690808</v>
+        <v>-5.148786329198042</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8006396403923746</v>
+        <v>0.7644653653894804</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.49863134919888</v>
+        <v>-0.6491273310155329</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.525157511863117</v>
+        <v>2.434859922773125</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240604.xlsx
+++ b/tame_output/ON/bt/strategyON_20240604.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-26.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,16 +926,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.7%</t>
+          <t>454.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-676.5%</t>
+          <t>-667.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-162.5%</t>
+          <t>186.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-299.8%</t>
+          <t>-296.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.5%</t>
+          <t>-155.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-288.9%</t>
+          <t>-273.8%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-202.5%</t>
+          <t>-161.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1984"/>
+  <dimension ref="A1:G1985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.908366367491769</v>
+        <v>-7.819144754228443</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07618665652536016</v>
+        <v>-0.04049801122002972</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.712666514136113</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>2.059916406303428</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.76042632608417</v>
+        <v>-7.671204712820844</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.136889562650488</v>
+        <v>-0.1012009173451576</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.692345598227555</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.952230033160395</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.743268175952876</v>
+        <v>-7.654046562689549</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1387402888514488</v>
+        <v>-0.103051643546118</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.675187448096261</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.953810936985693</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.699719769182185</v>
+        <v>-7.610498155918859</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1282815382382658</v>
+        <v>-0.09259289293293493</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.675187448096261</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.9468503248906</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.457571375728327</v>
+        <v>-7.368349762465001</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01695982647557948</v>
+        <v>0.01872881882975141</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.675187448096261</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.961312679271743</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.349312238605806</v>
+        <v>-7.260090625342479</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.02087594883262422</v>
+        <v>0.05656459413795512</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.675187448096261</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.955844799730938</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.226021103788675</v>
+        <v>-7.136799490525348</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06769049677005379</v>
+        <v>0.1033791420753842</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.55189631327913</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>2.027317574631793</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.204871904885231</v>
+        <v>-7.115650291621905</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08385115456875614</v>
+        <v>0.1195397998740866</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.530747114375687</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>2.047708072211185</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.961106462901787</v>
+        <v>-6.871884849638461</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1771380397091846</v>
+        <v>0.2128266850145151</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.530747114375687</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>2.043488780558235</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.859343642624492</v>
+        <v>-6.770122029361166</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2199674817401185</v>
+        <v>0.2556561270454489</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.517528045983258</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>2.053544535513709</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.609493248675418</v>
+        <v>-6.520271635412091</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3126497143034506</v>
+        <v>0.348338359608781</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.517528045983258</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>2.04628661049741</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.433601156207985</v>
+        <v>-6.344379542944658</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3866056748110722</v>
+        <v>0.4222943201164031</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.517528045983258</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>2.049885734018059</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.262154693185521</v>
+        <v>-6.172933079922195</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4685117660746116</v>
+        <v>0.5042004113799421</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.346081582960795</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.166081117886091</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.037121693516698</v>
+        <v>-5.947900080253372</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5575454435584377</v>
+        <v>0.5932340888637682</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.121048583291972</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.300121395303682</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.973485951282764</v>
+        <v>-5.884264338019437</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5876945415063286</v>
+        <v>0.6233831868116595</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.057412841058037</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.34299764169836</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.880485910076866</v>
+        <v>-5.791264296813539</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6060888167724836</v>
+        <v>0.6417774620778145</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.057412841058037</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.324191900482155</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.640055413272005</v>
+        <v>-5.550833800008679</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7040040921193054</v>
+        <v>0.7396927374246358</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.8169823442531772</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.470193275189949</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.567812845100811</v>
+        <v>-5.478591231837484</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7368304332226034</v>
+        <v>0.7725190785279339</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.8169823442531772</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.474122589024769</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.514814522819423</v>
+        <v>-5.425592909556096</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7587083460524986</v>
+        <v>0.794396991357829</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.7616460852512383</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.508002928343272</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.406009637339696</v>
+        <v>-5.316788024076369</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7992283714643826</v>
+        <v>0.8349170167697135</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.7616460852512383</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.505000999563266</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.185988839302685</v>
+        <v>-5.096767226039359</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.888815727689801</v>
+        <v>0.9245043729951319</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.6204262401832581</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.591311943614668</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.053121150239408</v>
+        <v>-4.963899536976081</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9578569861169353</v>
+        <v>0.9935456314222662</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.6204262401832581</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.607206126416491</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.893606046720038</v>
+        <v>-4.804384433456711</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.022808871964985</v>
+        <v>1.058497517270316</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.4609111366638882</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.704061032968415</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.7489339016203</v>
+        <v>-4.659712288356974</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.09076583256632</v>
+        <v>1.126454477871651</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.3162389915641508</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.800952422589698</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.808808728977993</v>
+        <v>-4.719587115714666</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.052853393024669</v>
+        <v>1.08854203833</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.3761138189218429</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.751065017576508</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.722009231198983</v>
+        <v>-4.632787617935657</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.109973685458839</v>
+        <v>1.145662330764169</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.3761138189218429</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.773465510899074</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.724478937660789</v>
+        <v>-4.635257324397463</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.109058204247529</v>
+        <v>1.144746849552859</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.378583525383649</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.772056088395403</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.7928491239848</v>
+        <v>-4.703627510721473</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.092717052192626</v>
+        <v>1.128405697497957</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3693078263474341</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.788628430291833</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.901387304900934</v>
+        <v>-4.812165691637607</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.039738488458064</v>
+        <v>1.075427133763395</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3693078263474341</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.779065138923725</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.932380464229639</v>
+        <v>-4.843158850966312</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8520507897669689</v>
+        <v>0.8877394350722994</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3693078263474341</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.603774703964111</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.75690620443717</v>
+        <v>-4.667684591173844</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9268077256757441</v>
+        <v>0.9624963709810748</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3693078263474341</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.608341935955899</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.867842457078419</v>
+        <v>-4.778620843815093</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8581752533804516</v>
+        <v>0.8938638986857823</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.3693078263474341</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.584083964717106</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.070869034621652</v>
+        <v>-4.981647421358326</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7800960075830639</v>
+        <v>0.8157846528883945</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5723344038906675</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.465399403411072</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.912943435686359</v>
+        <v>-4.823721822423033</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8534386335893134</v>
+        <v>0.889127278894644</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5723344038906675</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.475571789843204</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.826699972659982</v>
+        <v>-4.737478359396655</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8828822893737249</v>
+        <v>0.9185709346790554</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.5723344038906675</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.470518060417064</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.872006792058961</v>
+        <v>-4.782785178795635</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8565353370586584</v>
+        <v>0.892223982363989</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6131445668998983</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.437807738056052</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.901039896761263</v>
+        <v>-4.811818283497936</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8454739682108396</v>
+        <v>0.8811626135161701</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6131445668998983</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.438359611089153</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.808229415310403</v>
+        <v>-4.719007802047076</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8118708526825491</v>
+        <v>0.8475594979878798</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.5203340854490389</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.423318591851034</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.85261888463983</v>
+        <v>-4.763397271376504</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7959885408753788</v>
+        <v>0.8316771861807095</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.5647235547784666</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.398558386177979</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.73994766640358</v>
+        <v>-4.650726053140254</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.836132736681602</v>
+        <v>0.8718213819869325</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.4520523365422164</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.461236825631452</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.627570665220907</v>
+        <v>-4.538349051957581</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8865748329853385</v>
+        <v>0.9222634782906689</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.4520523365422164</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.466728121462119</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.825805234107638</v>
+        <v>-4.736583620844312</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8187782071991851</v>
+        <v>0.8544668525045158</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.650286905428947</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.35928458189862</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.910620947726552</v>
+        <v>-4.81958490186959</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6232076417522727</v>
+        <v>0.6596220600950575</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.8197635214746963</v>
+        <v>-0.6688577899561208</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.095954332271823</v>
+        <v>2.186497771182969</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.03768795403354</v>
+        <v>-4.946651908176579</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.692530499948683</v>
+        <v>0.7289449182914678</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.8197635214746963</v>
+        <v>-0.6688577899561208</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.216103992991029</v>
+        <v>2.306647431902174</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.124286537014643</v>
+        <v>-5.033250491157681</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6724040928585651</v>
+        <v>0.7088185112013496</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.8197635214746963</v>
+        <v>-0.6688577899561208</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.230617019093352</v>
+        <v>2.321160458004497</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.085902874456492</v>
+        <v>-4.99486682859953</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6851769992241943</v>
+        <v>0.7215914175669789</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7813798589165452</v>
+        <v>-0.6304741273979696</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.251066657970612</v>
+        <v>2.341610096881757</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.908786544421326</v>
+        <v>-4.817750498564364</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7527525600835625</v>
+        <v>0.7891669784263471</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7813798589165452</v>
+        <v>-0.6304741273979696</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.247795686815913</v>
+        <v>2.338339125727059</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.879084420445032</v>
+        <v>-4.788048374588071</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.765316801435993</v>
+        <v>0.8017312197787776</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7858499841318585</v>
+        <v>-0.6349442526132829</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.245797003448638</v>
+        <v>2.336340442359784</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.699708999206265</v>
+        <v>-4.608672953349303</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8308539452379144</v>
+        <v>0.867268363580699</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6290732259611398</v>
+        <v>-0.4781674944425642</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.333650033657484</v>
+        <v>2.424193472568629</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.744723212726871</v>
+        <v>-4.65368716686991</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7936557151612615</v>
+        <v>0.8300701335040461</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6594221212757444</v>
+        <v>-0.5085163897571688</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.296248151800311</v>
+        <v>2.386791590711456</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.011727722999306</v>
+        <v>-4.920691677142345</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6925454733912333</v>
+        <v>0.7289598917340179</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8537851593186929</v>
+        <v>-0.7028794278001174</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.185321891313488</v>
+        <v>2.275865330224633</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.112925504436479</v>
+        <v>-5.021889458579517</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6512702827128658</v>
+        <v>0.6876847010556504</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9221939728640121</v>
+        <v>-0.7712882413454365</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.143480525082798</v>
+        <v>2.234023963993943</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.080449918265707</v>
+        <v>-4.989413872408745</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6618604787354911</v>
+        <v>0.6982748970782759</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9221939728640121</v>
+        <v>-0.7712882413454365</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.141080486637114</v>
+        <v>2.23162392554826</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.06141179055841</v>
+        <v>-4.970375744701448</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6660004490266549</v>
+        <v>0.7024148673694397</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9803775841952066</v>
+        <v>-0.829471852676631</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.102695039046643</v>
+        <v>2.193238477957788</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.092538421709028</v>
+        <v>-5.001502375852066</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8311316655050884</v>
+        <v>0.867546083847873</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9803775841952066</v>
+        <v>-0.829471852676631</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.280276907985323</v>
+        <v>2.370820346896469</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.14485880230982</v>
+        <v>-5.053822756452858</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8110368422509051</v>
+        <v>0.8474512605936897</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9454307241863344</v>
+        <v>-0.7945249926677589</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.30207835297678</v>
+        <v>2.392621791887925</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.289181708234739</v>
+        <v>-5.198145662377777</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7593162102778637</v>
+        <v>0.7957306286206483</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9454307241863344</v>
+        <v>-0.7945249926677589</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.308086883373706</v>
+        <v>2.398630322284851</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.141438737999736</v>
+        <v>-5.050402692142774</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8975660461638864</v>
+        <v>0.9339804645066709</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7776233669514513</v>
+        <v>-0.6267176354328757</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.487923945506658</v>
+        <v>2.578467384417803</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.243453420530957</v>
+        <v>-5.152417374673996</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8595537946828791</v>
+        <v>0.8959682130256637</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7776233669514513</v>
+        <v>-0.6267176354328757</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.490717567038139</v>
+        <v>2.581261005949284</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.106844076436865</v>
+        <v>-5.015808030579903</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9148598807121742</v>
+        <v>0.9512742990549592</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6410140228573589</v>
+        <v>-0.4901082913387833</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.573345521886253</v>
+        <v>2.663888960797398</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.249609409259515</v>
+        <v>-5.158573363402553</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8568342243232245</v>
+        <v>0.8932486426660091</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7837793556800092</v>
+        <v>-0.6328736241614337</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.486766798932773</v>
+        <v>2.577310237843918</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.187311410483392</v>
+        <v>-5.096275364626431</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9480889776304942</v>
+        <v>0.9845033959732792</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7837793556800092</v>
+        <v>-0.6328736241614337</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.553102352729594</v>
+        <v>2.643645791640739</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.985521212818234</v>
+        <v>-4.894485166961273</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7373859290859555</v>
+        <v>0.7738003474287403</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5857611635108548</v>
+        <v>-0.4348554319922793</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.380494140420484</v>
+        <v>2.471037579331629</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.925630531175641</v>
+        <v>-4.83459448531868</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8316324340651682</v>
+        <v>0.8680468524079528</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5258704818682614</v>
+        <v>-0.3749647503496858</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.486718781728215</v>
+        <v>2.577262220639361</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.023371075800616</v>
+        <v>-4.932335029943654</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.807163952331222</v>
+        <v>0.8435783706740065</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5417597600012416</v>
+        <v>-0.390854028482666</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.491812950964471</v>
+        <v>2.582356389875616</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.199708835923545</v>
+        <v>-5.108672790066583</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7351648291067221</v>
+        <v>0.7715792474495067</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7180975201241711</v>
+        <v>-0.5671917886055954</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.384546275715385</v>
+        <v>2.47508971462653</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.199019463762322</v>
+        <v>-5.10798341790536</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7339321960111396</v>
+        <v>0.7703466143539246</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7180975201241711</v>
+        <v>-0.5671917886055954</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.383037893755314</v>
+        <v>2.473581332666459</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.205590428816914</v>
+        <v>-5.114554382959953</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.731166677424739</v>
+        <v>0.7675810957675235</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7246684851787639</v>
+        <v>-0.5737627536601884</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.378958182157994</v>
+        <v>2.469501621069139</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.197636458522142</v>
+        <v>-5.10660041266518</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7343482655426476</v>
+        <v>0.7707626838854322</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7246684851787639</v>
+        <v>-0.5737627536601884</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.378958182157994</v>
+        <v>2.469501621069139</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.187263082189055</v>
+        <v>-5.096227036332094</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7448793731036871</v>
+        <v>0.7812937914464717</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7142951088456766</v>
+        <v>-0.563389377327101</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.391563964985651</v>
+        <v>2.482107403896796</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.059578772394759</v>
+        <v>-4.968542726537797</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8008454703961303</v>
+        <v>0.8372598887389151</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5866107990513801</v>
+        <v>-0.4357050675328046</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.473066924236954</v>
+        <v>2.563610363148099</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.120245362797148</v>
+        <v>-5.029209316940186</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7633335067110472</v>
+        <v>0.7997479250538317</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6683091157699138</v>
+        <v>-0.5174033842513382</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.410802606681706</v>
+        <v>2.501346045592851</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.055251502863502</v>
+        <v>-4.96421545700654</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7934287532951338</v>
+        <v>0.8298431716379187</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6414785011657584</v>
+        <v>-0.4905727696471829</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.430998678054828</v>
+        <v>2.521542116965973</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.1560101386205</v>
+        <v>-5.064974092763538</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7572862386234127</v>
+        <v>0.7937006569661973</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7303040698927639</v>
+        <v>-0.5793983383741883</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.381864276449702</v>
+        <v>2.472407715360847</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.1118073015346</v>
+        <v>-5.020771255677638</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.78084697598561</v>
+        <v>0.8172613943283946</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6861012328068634</v>
+        <v>-0.5351955012882879</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.414265581229079</v>
+        <v>2.504809020140225</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,45 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.720666498268026</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.148786329198042</v>
+        <v>-5.058447266123579</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7644653653894804</v>
+        <v>0.8006009906192659</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6491273310155329</v>
+        <v>-0.4983407126936789</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.434859922773125</v>
+        <v>2.525331893766238</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="2" t="n">
+        <v>45447</v>
+      </c>
+      <c r="B1985" t="n">
+        <v>3.844184260677503</v>
+      </c>
+      <c r="C1985" t="n">
+        <v>2.850302515034977</v>
+      </c>
+      <c r="D1985" t="n">
+        <v>-5.058447266123579</v>
+      </c>
+      <c r="E1985" t="n">
+        <v>0.8006009906192659</v>
+      </c>
+      <c r="F1985" t="n">
+        <v>-0.4983407126936789</v>
+      </c>
+      <c r="G1985" t="n">
+        <v>2.843366312021345</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240604.xlsx
+++ b/tame_output/ON/bt/strategyON_20240604.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-34.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.3%</t>
+          <t>452.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-667.4%</t>
+          <t>-676.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>186.4%</t>
+          <t>-162.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-296.2%</t>
+          <t>-299.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.2%</t>
+          <t>-154.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.8%</t>
+          <t>-288.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-161.7%</t>
+          <t>-169.3%</t>
         </is>
       </c>
     </row>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.819144754228443</v>
+        <v>-7.908366367491769</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.04049801122002972</v>
+        <v>-0.07618665652536016</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.712666514136113</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.059916406303428</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.671204712820844</v>
+        <v>-7.76042632608417</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1012009173451576</v>
+        <v>-0.136889562650488</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.692345598227555</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.952230033160395</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.654046562689549</v>
+        <v>-7.743268175952876</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.103051643546118</v>
+        <v>-0.1387402888514488</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.675187448096261</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.953810936985693</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.610498155918859</v>
+        <v>-7.699719769182185</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.09259289293293493</v>
+        <v>-0.1282815382382658</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.675187448096261</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.9468503248906</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.368349762465001</v>
+        <v>-7.457571375728327</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.01872881882975141</v>
+        <v>-0.01695982647557948</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.675187448096261</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.961312679271743</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.260090625342479</v>
+        <v>-7.349312238605806</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05656459413795512</v>
+        <v>0.02087594883262422</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.675187448096261</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.955844799730938</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.136799490525348</v>
+        <v>-7.226021103788675</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1033791420753842</v>
+        <v>0.06769049677005379</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.55189631327913</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.027317574631793</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.115650291621905</v>
+        <v>-7.204871904885231</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1195397998740866</v>
+        <v>0.08385115456875614</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.530747114375687</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.047708072211185</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.871884849638461</v>
+        <v>-6.961106462901787</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2128266850145151</v>
+        <v>0.1771380397091846</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.530747114375687</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.043488780558235</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.770122029361166</v>
+        <v>-6.859343642624492</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2556561270454489</v>
+        <v>0.2199674817401185</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.517528045983258</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.053544535513709</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.520271635412091</v>
+        <v>-6.609493248675418</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.348338359608781</v>
+        <v>0.3126497143034506</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.517528045983258</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.04628661049741</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.344379542944658</v>
+        <v>-6.433601156207985</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4222943201164031</v>
+        <v>0.3866056748110722</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.517528045983258</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.049885734018059</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.172933079922195</v>
+        <v>-6.262154693185521</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5042004113799421</v>
+        <v>0.4685117660746116</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.346081582960795</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.166081117886091</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.947900080253372</v>
+        <v>-6.037121693516698</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5932340888637682</v>
+        <v>0.5575454435584377</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.121048583291972</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.300121395303682</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.884264338019437</v>
+        <v>-5.973485951282764</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6233831868116595</v>
+        <v>0.5876945415063286</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.057412841058037</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.34299764169836</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.791264296813539</v>
+        <v>-5.880485910076866</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6417774620778145</v>
+        <v>0.6060888167724836</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.057412841058037</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.324191900482155</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.550833800008679</v>
+        <v>-5.640055413272005</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7396927374246358</v>
+        <v>0.7040040921193054</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8169823442531772</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.470193275189949</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.478591231837484</v>
+        <v>-5.567812845100811</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7725190785279339</v>
+        <v>0.7368304332226034</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8169823442531772</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.474122589024769</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.425592909556096</v>
+        <v>-5.514814522819423</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.794396991357829</v>
+        <v>0.7587083460524986</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7616460852512383</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.508002928343272</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.316788024076369</v>
+        <v>-5.406009637339696</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8349170167697135</v>
+        <v>0.7992283714643826</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7616460852512383</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.505000999563266</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.096767226039359</v>
+        <v>-5.185988839302685</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9245043729951319</v>
+        <v>0.888815727689801</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6204262401832581</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.591311943614668</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.963899536976081</v>
+        <v>-5.053121150239408</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9935456314222662</v>
+        <v>0.9578569861169353</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6204262401832581</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.607206126416491</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.804384433456711</v>
+        <v>-4.893606046720038</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.058497517270316</v>
+        <v>1.022808871964985</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4609111366638882</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.704061032968415</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.659712288356974</v>
+        <v>-4.7489339016203</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.126454477871651</v>
+        <v>1.09076583256632</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3162389915641508</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.800952422589698</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.719587115714666</v>
+        <v>-4.808808728977993</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.08854203833</v>
+        <v>1.052853393024669</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3761138189218429</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.751065017576508</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.632787617935657</v>
+        <v>-4.722009231198983</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.145662330764169</v>
+        <v>1.109973685458839</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3761138189218429</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.773465510899074</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.635257324397463</v>
+        <v>-4.724478937660789</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.144746849552859</v>
+        <v>1.109058204247529</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.378583525383649</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.772056088395403</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.703627510721473</v>
+        <v>-4.7928491239848</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.128405697497957</v>
+        <v>1.092717052192626</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3693078263474341</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.788628430291833</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.812165691637607</v>
+        <v>-4.901387304900934</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.075427133763395</v>
+        <v>1.039738488458064</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3693078263474341</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.779065138923725</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.843158850966312</v>
+        <v>-4.932380464229639</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8877394350722994</v>
+        <v>0.8520507897669689</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3693078263474341</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.603774703964111</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.667684591173844</v>
+        <v>-4.75690620443717</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9624963709810748</v>
+        <v>0.9268077256757441</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3693078263474341</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.608341935955899</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.778620843815093</v>
+        <v>-4.867842457078419</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8938638986857823</v>
+        <v>0.8581752533804516</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3693078263474341</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.584083964717106</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.981647421358326</v>
+        <v>-5.070869034621652</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8157846528883945</v>
+        <v>0.7800960075830639</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5723344038906675</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.465399403411072</v>
+        <v>2.415393549788432</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.823721822423033</v>
+        <v>-4.912943435686359</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.889127278894644</v>
+        <v>0.8534386335893134</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5723344038906675</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.475571789843204</v>
+        <v>2.425565936220564</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.737478359396655</v>
+        <v>-4.826699972659982</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9185709346790554</v>
+        <v>0.8828822893737249</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5723344038906675</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.470518060417064</v>
+        <v>2.420512206794424</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.782785178795635</v>
+        <v>-4.872006792058961</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.892223982363989</v>
+        <v>0.8565353370586584</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6131445668998983</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.437807738056052</v>
+        <v>2.387801884433411</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.811818283497936</v>
+        <v>-4.901039896761263</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8811626135161701</v>
+        <v>0.8454739682108396</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6131445668998983</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.438359611089153</v>
+        <v>2.388353757466513</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.719007802047076</v>
+        <v>-4.808229415310403</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8475594979878798</v>
+        <v>0.8118708526825491</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5203340854490389</v>
+        <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.423318591851034</v>
+        <v>2.373312738228394</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.763397271376504</v>
+        <v>-4.85261888463983</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8316771861807095</v>
+        <v>0.7959885408753788</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5647235547784666</v>
+        <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.398558386177979</v>
+        <v>2.348552532555338</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.650726053140254</v>
+        <v>-4.73994766640358</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8718213819869325</v>
+        <v>0.836132736681602</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4520523365422164</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.461236825631452</v>
+        <v>2.411230972008811</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.538349051957581</v>
+        <v>-4.627570665220907</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9222634782906689</v>
+        <v>0.8865748329853385</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4520523365422164</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.466728121462119</v>
+        <v>2.416722267839479</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.736583620844312</v>
+        <v>-4.825805234107638</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8544668525045158</v>
+        <v>0.8187782071991851</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.650286905428947</v>
+        <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.35928458189862</v>
+        <v>2.309278728275979</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.81958490186959</v>
+        <v>-4.910620947726552</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6596220600950575</v>
+        <v>0.6232076417522727</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6688577899561208</v>
+        <v>-0.8197635214746963</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.186497771182969</v>
+        <v>2.095954332271823</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.946651908176579</v>
+        <v>-5.03768795403354</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7289449182914678</v>
+        <v>0.692530499948683</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6688577899561208</v>
+        <v>-0.8197635214746963</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.306647431902174</v>
+        <v>2.216103992991029</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.033250491157681</v>
+        <v>-5.124286537014643</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7088185112013496</v>
+        <v>0.6724040928585651</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6688577899561208</v>
+        <v>-0.8197635214746963</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.321160458004497</v>
+        <v>2.230617019093352</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.99486682859953</v>
+        <v>-5.085902874456492</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7215914175669789</v>
+        <v>0.6851769992241943</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.6304741273979696</v>
+        <v>-0.7813798589165452</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.341610096881757</v>
+        <v>2.251066657970612</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.817750498564364</v>
+        <v>-4.908786544421326</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7891669784263471</v>
+        <v>0.7527525600835625</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.6304741273979696</v>
+        <v>-0.7813798589165452</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.338339125727059</v>
+        <v>2.247795686815913</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.788048374588071</v>
+        <v>-4.879084420445032</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8017312197787776</v>
+        <v>0.765316801435993</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.6349442526132829</v>
+        <v>-0.7858499841318585</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.336340442359784</v>
+        <v>2.245797003448638</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.608672953349303</v>
+        <v>-4.699708999206265</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.867268363580699</v>
+        <v>0.8308539452379144</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4781674944425642</v>
+        <v>-0.6290732259611398</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.424193472568629</v>
+        <v>2.333650033657484</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.65368716686991</v>
+        <v>-4.744723212726871</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8300701335040461</v>
+        <v>0.7936557151612615</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.5085163897571688</v>
+        <v>-0.6594221212757444</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.386791590711456</v>
+        <v>2.296248151800311</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.920691677142345</v>
+        <v>-5.011727722999306</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7289598917340179</v>
+        <v>0.6925454733912333</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7028794278001174</v>
+        <v>-0.8537851593186929</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.275865330224633</v>
+        <v>2.185321891313488</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.021889458579517</v>
+        <v>-5.112925504436479</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6876847010556504</v>
+        <v>0.6512702827128658</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7712882413454365</v>
+        <v>-0.9221939728640121</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.234023963993943</v>
+        <v>2.143480525082798</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.989413872408745</v>
+        <v>-5.080449918265707</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6982748970782759</v>
+        <v>0.6618604787354911</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7712882413454365</v>
+        <v>-0.9221939728640121</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.23162392554826</v>
+        <v>2.141080486637114</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.970375744701448</v>
+        <v>-5.06141179055841</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7024148673694397</v>
+        <v>0.6660004490266549</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.829471852676631</v>
+        <v>-0.9803775841952066</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.193238477957788</v>
+        <v>2.102695039046643</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.001502375852066</v>
+        <v>-5.092538421709028</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.867546083847873</v>
+        <v>0.8311316655050884</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.829471852676631</v>
+        <v>-0.9803775841952066</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.370820346896469</v>
+        <v>2.280276907985323</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.053822756452858</v>
+        <v>-5.14485880230982</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8474512605936897</v>
+        <v>0.8110368422509051</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7945249926677589</v>
+        <v>-0.9454307241863344</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.392621791887925</v>
+        <v>2.30207835297678</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.198145662377777</v>
+        <v>-5.289181708234739</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7957306286206483</v>
+        <v>0.7593162102778637</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7945249926677589</v>
+        <v>-0.9454307241863344</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.398630322284851</v>
+        <v>2.308086883373706</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.050402692142774</v>
+        <v>-5.141438737999736</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9339804645066709</v>
+        <v>0.8975660461638864</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.6267176354328757</v>
+        <v>-0.7776233669514513</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.578467384417803</v>
+        <v>2.487923945506658</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.152417374673996</v>
+        <v>-5.243453420530957</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8959682130256637</v>
+        <v>0.8595537946828791</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.6267176354328757</v>
+        <v>-0.7776233669514513</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.581261005949284</v>
+        <v>2.490717567038139</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.015808030579903</v>
+        <v>-5.106844076436865</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9512742990549592</v>
+        <v>0.9148598807121742</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4901082913387833</v>
+        <v>-0.6410140228573589</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.663888960797398</v>
+        <v>2.573345521886253</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.158573363402553</v>
+        <v>-5.249609409259515</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8932486426660091</v>
+        <v>0.8568342243232245</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6328736241614337</v>
+        <v>-0.7837793556800092</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.577310237843918</v>
+        <v>2.486766798932773</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.096275364626431</v>
+        <v>-5.187311410483392</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9845033959732792</v>
+        <v>0.9480889776304942</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6328736241614337</v>
+        <v>-0.7837793556800092</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.643645791640739</v>
+        <v>2.553102352729594</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.894485166961273</v>
+        <v>-4.985521212818234</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7738003474287403</v>
+        <v>0.7373859290859555</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.4348554319922793</v>
+        <v>-0.5857611635108548</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.471037579331629</v>
+        <v>2.380494140420484</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.83459448531868</v>
+        <v>-4.925630531175641</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8680468524079528</v>
+        <v>0.8316324340651682</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3749647503496858</v>
+        <v>-0.5258704818682614</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.577262220639361</v>
+        <v>2.486718781728215</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.932335029943654</v>
+        <v>-5.023371075800616</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8435783706740065</v>
+        <v>0.807163952331222</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.390854028482666</v>
+        <v>-0.5417597600012416</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.582356389875616</v>
+        <v>2.491812950964471</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.108672790066583</v>
+        <v>-5.199708835923545</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7715792474495067</v>
+        <v>0.7351648291067221</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.5671917886055954</v>
+        <v>-0.7180975201241711</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.47508971462653</v>
+        <v>2.384546275715385</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.10798341790536</v>
+        <v>-5.199019463762322</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7703466143539246</v>
+        <v>0.7339321960111396</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.5671917886055954</v>
+        <v>-0.7180975201241711</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.473581332666459</v>
+        <v>2.383037893755314</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.114554382959953</v>
+        <v>-5.205590428816914</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7675810957675235</v>
+        <v>0.731166677424739</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5737627536601884</v>
+        <v>-0.7246684851787639</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.469501621069139</v>
+        <v>2.378958182157994</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.10660041266518</v>
+        <v>-5.197636458522142</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7707626838854322</v>
+        <v>0.7343482655426476</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5737627536601884</v>
+        <v>-0.7246684851787639</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.469501621069139</v>
+        <v>2.378958182157994</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.096227036332094</v>
+        <v>-5.187263082189055</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7812937914464717</v>
+        <v>0.7448793731036871</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.563389377327101</v>
+        <v>-0.7142951088456766</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.482107403896796</v>
+        <v>2.391563964985651</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.968542726537797</v>
+        <v>-5.059578772394759</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8372598887389151</v>
+        <v>0.8008454703961303</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.4357050675328046</v>
+        <v>-0.5866107990513801</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.563610363148099</v>
+        <v>2.473066924236954</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.029209316940186</v>
+        <v>-5.120245362797148</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7997479250538317</v>
+        <v>0.7633335067110472</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.5174033842513382</v>
+        <v>-0.6683091157699138</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.501346045592851</v>
+        <v>2.410802606681706</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.96421545700654</v>
+        <v>-5.055251502863502</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8298431716379187</v>
+        <v>0.7934287532951338</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4905727696471829</v>
+        <v>-0.6414785011657584</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.521542116965973</v>
+        <v>2.430998678054828</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.064974092763538</v>
+        <v>-5.1560101386205</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7937006569661973</v>
+        <v>0.7572862386234127</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5793983383741883</v>
+        <v>-0.7303040698927639</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.472407715360847</v>
+        <v>2.381864276449702</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.020771255677638</v>
+        <v>-5.1118073015346</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8172613943283946</v>
+        <v>0.78084697598561</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.5351955012882879</v>
+        <v>-0.6861012328068634</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.504809020140225</v>
+        <v>2.414265581229079</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.058447266123579</v>
+        <v>-5.148786329198042</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8006009906192659</v>
+        <v>0.7644653653894804</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4983407126936789</v>
+        <v>-0.6491273310155329</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.525331893766238</v>
+        <v>2.434859922773125</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.844184260677503</v>
+        <v>3.722004802523401</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.850302515034977</v>
+        <v>2.774430929660998</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.058447266123579</v>
+        <v>-5.148786329198042</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8006009906192659</v>
+        <v>0.7644653653894804</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.4983407126936789</v>
+        <v>-0.6491273310155329</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.843366312021345</v>
+        <v>2.767494726647366</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240604.xlsx
+++ b/tame_output/ON/bt/strategyON_20240604.xlsx
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.722004802523401</v>
+        <v>3.722004802523402</v>
       </c>
       <c r="C1985" t="n">
         <v>2.774430929660998</v>

--- a/tame_output/ON/bt/strategyON_20240604.xlsx
+++ b/tame_output/ON/bt/strategyON_20240604.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-58.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-81.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.7%</t>
+          <t>448.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-676.5%</t>
+          <t>-699.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-162.5%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-299.8%</t>
+          <t>-309.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.5%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-288.9%</t>
+          <t>-282.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.3%</t>
+          <t>-193.2%</t>
         </is>
       </c>
     </row>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.91035543111305</v>
+        <v>-11.14363552462742</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185754406644191</v>
+        <v>-1.279066444049936</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.887920473006568</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.445991906310837</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78577677477546</v>
+        <v>-11.01905686828982</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134783799553095</v>
+        <v>-1.228095836958841</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.887920473006568</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.447131050866896</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83867206281974</v>
+        <v>-11.07195215633411</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.153308140608702</v>
+        <v>-1.246620178014448</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.882965126918121</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.452738032682071</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.554763331891</v>
+        <v>-10.78804342540536</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.034010943998566</v>
+        <v>-1.127322981404312</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.882965126918121</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.458471736920707</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.48339693928135</v>
+        <v>-10.71667703279571</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.015201649348572</v>
+        <v>-1.108513686754318</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.811598734308473</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.491554310092631</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.21956007207728</v>
+        <v>-10.45284016559164</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.919550383779852</v>
+        <v>-1.012862421185598</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.811598734308473</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.481670828779724</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.952318271208881</v>
+        <v>-10.18559836472325</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8144882239318663</v>
+        <v>-0.9078002613376124</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.811598734308473</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.47983626828035</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.85441123253239</v>
+        <v>-10.08769132604676</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.775625723434731</v>
+        <v>-0.8689377608404771</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.743612984447917</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.520327403223223</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.830457691556433</v>
+        <v>-10.0637377850708</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.765375800898854</v>
+        <v>-0.8586878383046002</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.719659443471959</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.535368033954291</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.566397753233636</v>
+        <v>-9.799677846748001</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6730121417314878</v>
+        <v>-0.7663241791372335</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.455599505149163</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.680543680786216</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.859318129728798</v>
+        <v>-9.092598223243163</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3929673259898534</v>
+        <v>-0.4862793633955995</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.455599505149163</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.677756647125916</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.819133831362608</v>
+        <v>-9.052413924876973</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3765499827555359</v>
+        <v>-0.469862020161282</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.415415206782972</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.702210850033471</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.739064035824804</v>
+        <v>-8.972344129339168</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3451552433196574</v>
+        <v>-0.4384672807254031</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.335345411245168</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.749619548576911</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.505582813595204</v>
+        <v>-8.738862907109571</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.243838325589965</v>
+        <v>-0.337150362995712</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-2.10186418901557</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.897632710752522</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.35591642258769</v>
+        <v>-8.589196516102056</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1868639794999187</v>
+        <v>-0.2801760169056653</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-2.008960697773034</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>1.950482595185084</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.223640948956803</v>
+        <v>-8.456921042471169</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1385863033005368</v>
+        <v>-0.2318983407062833</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-1.876685224142147</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>2.025215366110643</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.033041274283649</v>
+        <v>-8.266321367798016</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0595313727436384</v>
+        <v>-0.1528434101493854</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.686085549468995</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.142390231602172</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.784041475600068</v>
+        <v>-8.017321569114435</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.0529748879534524</v>
+        <v>-0.04033714945229416</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.686085549468995</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.155296572825831</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.889631465373173</v>
+        <v>-8.122911558887539</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1172370375550078</v>
+        <v>-0.2105490749607544</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.791675539242099</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>1.963966649362749</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.908366367491769</v>
+        <v>-8.141646461006136</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07618665652536016</v>
+        <v>-0.1694986939311072</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.79727154890223</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>2.009153385443757</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.76042632608417</v>
+        <v>-7.993706419598537</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.136889562650488</v>
+        <v>-0.230201600056235</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.776950632993673</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>1.901467012300724</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.743268175952876</v>
+        <v>-7.976548269467242</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1387402888514488</v>
+        <v>-0.2320523262571954</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.759792482862378</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>1.903047916126023</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.699719769182185</v>
+        <v>-7.932999862696552</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1282815382382658</v>
+        <v>-0.2215935756440124</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.759792482862378</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>1.896087304030929</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.457571375728327</v>
+        <v>-7.690851469242694</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01695982647557948</v>
+        <v>-0.110271863881326</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.759792482862378</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>1.910549658412072</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.349312238605806</v>
+        <v>-7.582592332120172</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.02087594883262422</v>
+        <v>-0.07243608857312234</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.759792482862378</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>1.905081778871268</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.226021103788675</v>
+        <v>-7.459301197303041</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06769049677005379</v>
+        <v>-0.02562154063569322</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.636501348045248</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>1.976554553772123</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.204871904885231</v>
+        <v>-7.438151998399598</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08385115456875614</v>
+        <v>-0.009460882836990425</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.615352149141805</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>1.996945051351514</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.961106462901787</v>
+        <v>-7.194386556416154</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1771380397091846</v>
+        <v>0.08382600230343806</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.615352149141805</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>1.992725759698565</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.859343642624492</v>
+        <v>-7.092623736138859</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2199674817401185</v>
+        <v>0.1266554443343719</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.602133080749376</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>2.002781514654038</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.609493248675418</v>
+        <v>-6.842773342189784</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3126497143034506</v>
+        <v>0.219337676897704</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.602133080749376</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>1.99552358963774</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.433601156207985</v>
+        <v>-6.666881249722351</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3866056748110722</v>
+        <v>0.2932936374053257</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.602133080749376</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>1.999122713158389</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.262154693185521</v>
+        <v>-6.495434786699888</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4685117660746116</v>
+        <v>0.3751997286688646</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.430686617726913</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.11531809702642</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.037121693516698</v>
+        <v>-6.270401787031065</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5575454435584377</v>
+        <v>0.4642334061526912</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.20565361805809</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.249358374444011</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.973485951282764</v>
+        <v>-6.20676604479713</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5876945415063286</v>
+        <v>0.494382504100582</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.142017875824155</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.292234620838689</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.880485910076866</v>
+        <v>-6.113766003591232</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6060888167724836</v>
+        <v>0.512776779366737</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.142017875824155</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.273428879622485</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.640055413272005</v>
+        <v>-5.873335506786372</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7040040921193054</v>
+        <v>0.6106920547135584</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.901587379019295</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.419430254330278</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.567812845100811</v>
+        <v>-5.801092938615177</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7368304332226034</v>
+        <v>0.6435183958168564</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.901587379019295</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.423359568165098</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.514814522819423</v>
+        <v>-5.748094616333789</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7587083460524986</v>
+        <v>0.6653963086467516</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.8462511200173561</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.457239907483602</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.406009637339696</v>
+        <v>-5.639289730854062</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7992283714643826</v>
+        <v>0.7059163340586361</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.8462511200173561</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.454237978703595</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.185988839302685</v>
+        <v>-5.419268932817052</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.888815727689801</v>
+        <v>0.7955036902840544</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7050312749493759</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.540548922754997</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.053121150239408</v>
+        <v>-5.286401243753774</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9578569861169353</v>
+        <v>0.8645449487111887</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7050312749493759</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.55644310555682</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.893606046720038</v>
+        <v>-5.126886140234404</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.022808871964985</v>
+        <v>0.9294968345592385</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.545516171430006</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.653298012108745</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.7489339016203</v>
+        <v>-4.982213995134667</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.09076583256632</v>
+        <v>0.9974537951605735</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.4008440263302686</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.750189401730027</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.808808728977993</v>
+        <v>-5.042088822492359</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.052853393024669</v>
+        <v>0.9595413556189225</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.4607188536879607</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.700301996716837</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.722009231198983</v>
+        <v>-4.95528932471335</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.109973685458839</v>
+        <v>1.016661648053092</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.4607188536879607</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.722702490039403</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.724478937660789</v>
+        <v>-4.957759031175156</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.109058204247529</v>
+        <v>1.015746166841782</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.4631885601497668</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.721293067535732</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.7928491239848</v>
+        <v>-5.026129217499166</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.092717052192626</v>
+        <v>0.9994050147868796</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4539128611135519</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.737865409432163</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.901387304900934</v>
+        <v>-5.1346673984153</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.039738488458064</v>
+        <v>0.9464264510523175</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4539128611135519</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.728302118064054</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.932380464229639</v>
+        <v>-5.165660557744006</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8520507897669689</v>
+        <v>0.7587387523612223</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4539128611135519</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.553011683104441</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.75690620443717</v>
+        <v>-4.990186297951537</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9268077256757441</v>
+        <v>0.8334956882699975</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4539128611135519</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.557578915096228</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.867842457078419</v>
+        <v>-5.101122550592786</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8581752533804516</v>
+        <v>0.7648632159747049</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.4539128611135519</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.533320943857436</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.070869034621652</v>
+        <v>-5.304149128136019</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7800960075830639</v>
+        <v>0.6867839701773173</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.6569394386567853</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.414636382551401</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.912943435686359</v>
+        <v>-5.146223529200726</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8534386335893134</v>
+        <v>0.7601265961835666</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.6569394386567853</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.424808768983534</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.826699972659982</v>
+        <v>-5.059980066174348</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8828822893737249</v>
+        <v>0.7895702519679784</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.6569394386567853</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.419755039557394</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.872006792058961</v>
+        <v>-5.105286885573328</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8565353370586584</v>
+        <v>0.7632232996529118</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6977496016660161</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.387044717196381</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.901039896761263</v>
+        <v>-5.134319990275629</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8454739682108396</v>
+        <v>0.7521619308050931</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.6977496016660161</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.387596590229482</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.808229415310403</v>
+        <v>-5.041509508824769</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8118708526825491</v>
+        <v>0.7185588152768023</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.6049391202151567</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.372555570991364</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.85261888463983</v>
+        <v>-5.085898978154197</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7959885408753788</v>
+        <v>0.7026765034696321</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.6493285895445844</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.347795365318308</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.73994766640358</v>
+        <v>-4.973227759917947</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.836132736681602</v>
+        <v>0.7428206992758553</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5366573713083342</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.410473804771781</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.627570665220907</v>
+        <v>-4.860850758735274</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8865748329853385</v>
+        <v>0.7932627955795917</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5366573713083342</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.415965100602449</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.825805234107638</v>
+        <v>-5.059085327622005</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8187782071991851</v>
+        <v>0.7254661697934384</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.7348919401950649</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.308521561038949</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.910620947726552</v>
+        <v>-5.142086608647284</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6232076417522727</v>
+        <v>0.5306213773839801</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.8197635214746963</v>
+        <v>-0.7534628247222386</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.095954332271823</v>
+        <v>2.135734750323298</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.03768795403354</v>
+        <v>-5.269153614954272</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.692530499948683</v>
+        <v>0.5999442355803906</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.8197635214746963</v>
+        <v>-0.7534628247222386</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.216103992991029</v>
+        <v>2.255884411042504</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.124286537014643</v>
+        <v>-5.355752197935375</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6724040928585651</v>
+        <v>0.5798178284902722</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.8197635214746963</v>
+        <v>-0.7534628247222386</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.230617019093352</v>
+        <v>2.270397437144827</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.085902874456492</v>
+        <v>-5.317368535377224</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6851769992241943</v>
+        <v>0.5925907348559014</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7813798589165452</v>
+        <v>-0.7150791621640874</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.251066657970612</v>
+        <v>2.290847076022086</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.908786544421326</v>
+        <v>-5.140252205342057</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7527525600835625</v>
+        <v>0.6601662957152699</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7813798589165452</v>
+        <v>-0.7150791621640874</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.247795686815913</v>
+        <v>2.287576104867388</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.879084420445032</v>
+        <v>-5.110550081365764</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.765316801435993</v>
+        <v>0.6727305370677006</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7858499841318585</v>
+        <v>-0.7195492873794007</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.245797003448638</v>
+        <v>2.285577421500113</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.699708999206265</v>
+        <v>-4.931174660126996</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8308539452379144</v>
+        <v>0.7382676808696218</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6290732259611398</v>
+        <v>-0.562772529208682</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.333650033657484</v>
+        <v>2.373430451708959</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.744723212726871</v>
+        <v>-4.976188873647603</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7936557151612615</v>
+        <v>0.7010694507929689</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6594221212757444</v>
+        <v>-0.5931214245232866</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.296248151800311</v>
+        <v>2.336028569851786</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.011727722999306</v>
+        <v>-5.243193383920038</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6925454733912333</v>
+        <v>0.5999592090229409</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8537851593186929</v>
+        <v>-0.7874844625662352</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.185321891313488</v>
+        <v>2.225102309364962</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.112925504436479</v>
+        <v>-5.34439116535721</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6512702827128658</v>
+        <v>0.5586840183445729</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9221939728640121</v>
+        <v>-0.8558932761115543</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.143480525082798</v>
+        <v>2.183260943134272</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.080449918265707</v>
+        <v>-5.311915579186438</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6618604787354911</v>
+        <v>0.5692742143671987</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9221939728640121</v>
+        <v>-0.8558932761115543</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.141080486637114</v>
+        <v>2.180860904688589</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.06141179055841</v>
+        <v>-5.292877451479141</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6660004490266549</v>
+        <v>0.5734141846583625</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9803775841952066</v>
+        <v>-0.9140768874427488</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.102695039046643</v>
+        <v>2.142475457098117</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.092538421709028</v>
+        <v>-5.324004082629759</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8311316655050884</v>
+        <v>0.7385454011367956</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9803775841952066</v>
+        <v>-0.9140768874427488</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.280276907985323</v>
+        <v>2.320057326036798</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.14485880230982</v>
+        <v>-5.376324463230551</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8110368422509051</v>
+        <v>0.7184505778826127</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9454307241863344</v>
+        <v>-0.8791300274338767</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.30207835297678</v>
+        <v>2.341858771028255</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.289181708234739</v>
+        <v>-5.52064736915547</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7593162102778637</v>
+        <v>0.6667299459095708</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9454307241863344</v>
+        <v>-0.8791300274338767</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.308086883373706</v>
+        <v>2.347867301425181</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.141438737999736</v>
+        <v>-5.372904398920467</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8975660461638864</v>
+        <v>0.8049797817955939</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7776233669514513</v>
+        <v>-0.7113226701989935</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.487923945506658</v>
+        <v>2.527704363558132</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.243453420530957</v>
+        <v>-5.474919081451689</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8595537946828791</v>
+        <v>0.7669675303145862</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7776233669514513</v>
+        <v>-0.7113226701989935</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.490717567038139</v>
+        <v>2.530497985089613</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.106844076436865</v>
+        <v>-5.338309737357596</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9148598807121742</v>
+        <v>0.8222736163438817</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6410140228573589</v>
+        <v>-0.5747133261049011</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.573345521886253</v>
+        <v>2.613125939937727</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.249609409259515</v>
+        <v>-5.481075070180246</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8568342243232245</v>
+        <v>0.7642479599549321</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7837793556800092</v>
+        <v>-0.7174786589275515</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.486766798932773</v>
+        <v>2.526547216984247</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.187311410483392</v>
+        <v>-5.418777071404124</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9480889776304942</v>
+        <v>0.8555027132622017</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7837793556800092</v>
+        <v>-0.7174786589275515</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.553102352729594</v>
+        <v>2.592882770781068</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.985521212818234</v>
+        <v>-5.216986873738966</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7373859290859555</v>
+        <v>0.644799664717663</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5857611635108548</v>
+        <v>-0.5194604667583971</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.380494140420484</v>
+        <v>2.420274558471959</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.925630531175641</v>
+        <v>-5.157096192096373</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8316324340651682</v>
+        <v>0.7390461696968753</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5258704818682614</v>
+        <v>-0.4595697851158036</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.486718781728215</v>
+        <v>2.52649919977969</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.023371075800616</v>
+        <v>-5.254836736721347</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.807163952331222</v>
+        <v>0.7145776879629295</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5417597600012416</v>
+        <v>-0.4754590632487838</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.491812950964471</v>
+        <v>2.531593369015946</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.199708835923545</v>
+        <v>-5.431174496844276</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7351648291067221</v>
+        <v>0.6425785647384292</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7180975201241711</v>
+        <v>-0.6517968233717132</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.384546275715385</v>
+        <v>2.42432669376686</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.199019463762322</v>
+        <v>-5.430485124683053</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7339321960111396</v>
+        <v>0.6413459316428471</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7180975201241711</v>
+        <v>-0.6517968233717132</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.383037893755314</v>
+        <v>2.422818311806788</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.205590428816914</v>
+        <v>-5.437056089737646</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.731166677424739</v>
+        <v>0.6385804130564461</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7246684851787639</v>
+        <v>-0.6583677884263062</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.378958182157994</v>
+        <v>2.418738600209469</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.197636458522142</v>
+        <v>-5.429102119442874</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7343482655426476</v>
+        <v>0.6417620011743552</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7246684851787639</v>
+        <v>-0.6583677884263062</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.378958182157994</v>
+        <v>2.418738600209469</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.187263082189055</v>
+        <v>-5.418728743109787</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7448793731036871</v>
+        <v>0.6522931087353947</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7142951088456766</v>
+        <v>-0.6479944120932188</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.391563964985651</v>
+        <v>2.431344383037126</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.059578772394759</v>
+        <v>-5.29104443331549</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8008454703961303</v>
+        <v>0.7082592060278379</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5866107990513801</v>
+        <v>-0.5203101022989224</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.473066924236954</v>
+        <v>2.512847342288429</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.120245362797148</v>
+        <v>-5.351711023717879</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7633335067110472</v>
+        <v>0.6707472423427547</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6683091157699138</v>
+        <v>-0.6020084190174561</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.410802606681706</v>
+        <v>2.45058302473318</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.055251502863502</v>
+        <v>-5.286717163784234</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7934287532951338</v>
+        <v>0.7008424889268414</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6414785011657584</v>
+        <v>-0.5751778044133007</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.430998678054828</v>
+        <v>2.470779096106302</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.1560101386205</v>
+        <v>-5.387475799541232</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7572862386234127</v>
+        <v>0.6646999742551203</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7303040698927639</v>
+        <v>-0.6640033731403061</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.381864276449702</v>
+        <v>2.421644694501177</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.1118073015346</v>
+        <v>-5.343272962455331</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.78084697598561</v>
+        <v>0.6882607116173176</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6861012328068634</v>
+        <v>-0.6198005360544057</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.414265581229079</v>
+        <v>2.454045999280554</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.148786329198042</v>
+        <v>-5.380251990118774</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7644653653894804</v>
+        <v>0.671879101021188</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6491273310155329</v>
+        <v>-0.5828266342630751</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.434859922773125</v>
+        <v>2.4746403408246</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.722004802523402</v>
+        <v>3.415031657143786</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.774430929660998</v>
+        <v>2.535590206071816</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.148786329198042</v>
+        <v>-5.380251990118774</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7644653653894804</v>
+        <v>0.671879101021188</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6491273310155329</v>
+        <v>-0.5828266342630751</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.767494726647366</v>
+        <v>2.528654003058184</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240604.xlsx
+++ b/tame_output/ON/bt/strategyON_20240604.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,55 +811,55 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-58.1%</t>
+          <t>-29.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.2%</t>
+          <t>-80.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>454.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-699.6%</t>
+          <t>-674.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.6%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-162.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-309.0%</t>
+          <t>-299.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-154.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-282.3%</t>
+          <t>-292.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-193.2%</t>
+          <t>-204.9%</t>
         </is>
       </c>
     </row>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.14363552462742</v>
+        <v>-10.91035543111305</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.279066444049936</v>
+        <v>-1.185754406644191</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.887920473006568</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.445991906310837</v>
+        <v>1.446749073547867</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.01905686828982</v>
+        <v>-10.78577677477546</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.228095836958841</v>
+        <v>-1.134783799553095</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.887920473006568</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447131050866896</v>
+        <v>1.447888218103926</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.07195215633411</v>
+        <v>-10.83867206281974</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.246620178014448</v>
+        <v>-1.153308140608702</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.882965126918121</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.452738032682071</v>
+        <v>1.453495199919101</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.78804342540536</v>
+        <v>-10.554763331891</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.127322981404312</v>
+        <v>-1.034010943998566</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.882965126918121</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.458471736920707</v>
+        <v>1.459228904157738</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.71667703279571</v>
+        <v>-10.48339693928135</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.108513686754318</v>
+        <v>-1.015201649348572</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.811598734308473</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.491554310092631</v>
+        <v>1.492311477329662</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.45284016559164</v>
+        <v>-10.21956007207728</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.012862421185598</v>
+        <v>-0.919550383779852</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.811598734308473</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.481670828779724</v>
+        <v>1.482427996016754</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.18559836472325</v>
+        <v>-9.952318271208881</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9078002613376124</v>
+        <v>-0.8144882239318663</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.811598734308473</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.47983626828035</v>
+        <v>1.48059343551738</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.08769132604676</v>
+        <v>-9.85441123253239</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8689377608404771</v>
+        <v>-0.775625723434731</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.743612984447917</v>
+        <v>-2.742351039052866</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.520327403223223</v>
+        <v>1.521084570460253</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.0637377850708</v>
+        <v>-9.830457691556433</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8586878383046002</v>
+        <v>-0.765375800898854</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.719659443471959</v>
+        <v>-2.718397498076909</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.535368033954291</v>
+        <v>1.536125201191321</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.799677846748001</v>
+        <v>-9.566397753233636</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7663241791372335</v>
+        <v>-0.6730121417314878</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.455599505149163</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.680543680786216</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.092598223243163</v>
+        <v>-8.859318129728798</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4862793633955995</v>
+        <v>-0.3929673259898534</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.455599505149163</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.677756647125916</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.052413924876973</v>
+        <v>-8.819133831362608</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.469862020161282</v>
+        <v>-0.3765499827555359</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.415415206782972</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702210850033471</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.972344129339168</v>
+        <v>-8.739064035824804</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4384672807254031</v>
+        <v>-0.3451552433196574</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.335345411245168</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.749619548576911</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.738862907109571</v>
+        <v>-8.505582813595204</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.337150362995712</v>
+        <v>-0.243838325589965</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.10186418901557</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.897632710752522</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.589196516102056</v>
+        <v>-8.35591642258769</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2801760169056653</v>
+        <v>-0.1868639794999187</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.008960697773034</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.950482595185084</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.456921042471169</v>
+        <v>-8.223640948956803</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2318983407062833</v>
+        <v>-0.1385863033005368</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.876685224142147</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025215366110643</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.266321367798016</v>
+        <v>-8.033041274283649</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1528434101493854</v>
+        <v>-0.0595313727436384</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.686085549468995</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.142390231602172</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.017321569114435</v>
+        <v>-7.784041475600068</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.04033714945229416</v>
+        <v>0.0529748879534524</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.686085549468995</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.155296572825831</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.122911558887539</v>
+        <v>-7.889631465373173</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2105490749607544</v>
+        <v>-0.1172370375550078</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.791675539242099</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.963966649362749</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.141646461006136</v>
+        <v>-7.908366367491769</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1694986939311072</v>
+        <v>-0.07618665652536016</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79727154890223</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009153385443757</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.993706419598537</v>
+        <v>-7.76042632608417</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.230201600056235</v>
+        <v>-0.136889562650488</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.776950632993673</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.901467012300724</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.976548269467242</v>
+        <v>-7.743268175952876</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2320523262571954</v>
+        <v>-0.1387402888514488</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.759792482862378</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903047916126023</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.932999862696552</v>
+        <v>-7.699719769182185</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2215935756440124</v>
+        <v>-0.1282815382382658</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.759792482862378</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.896087304030929</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.690851469242694</v>
+        <v>-7.457571375728327</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.110271863881326</v>
+        <v>-0.01695982647557948</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.759792482862378</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.910549658412072</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.582592332120172</v>
+        <v>-7.349312238605806</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.07243608857312234</v>
+        <v>0.02087594883262422</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.759792482862378</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905081778871268</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.459301197303041</v>
+        <v>-7.226021103788675</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.02562154063569322</v>
+        <v>0.06769049677005379</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.636501348045248</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.976554553772123</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.438151998399598</v>
+        <v>-7.204871904885231</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.009460882836990425</v>
+        <v>0.08385115456875614</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.615352149141805</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.996945051351514</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.194386556416154</v>
+        <v>-6.961106462901787</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.08382600230343806</v>
+        <v>0.1771380397091846</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.615352149141805</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.992725759698565</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.092623736138859</v>
+        <v>-6.859343642624492</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1266554443343719</v>
+        <v>0.2199674817401185</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.602133080749376</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.002781514654038</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.842773342189784</v>
+        <v>-6.609493248675418</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.219337676897704</v>
+        <v>0.3126497143034506</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.602133080749376</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99552358963774</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.666881249722351</v>
+        <v>-6.433601156207985</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2932936374053257</v>
+        <v>0.3866056748110722</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.602133080749376</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999122713158389</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.495434786699888</v>
+        <v>-6.262154693185521</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3751997286688646</v>
+        <v>0.4685117660746116</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.430686617726913</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.11531809702642</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.270401787031065</v>
+        <v>-6.037121693516698</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4642334061526912</v>
+        <v>0.5575454435584377</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.20565361805809</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.249358374444011</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.20676604479713</v>
+        <v>-5.973485951282764</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.494382504100582</v>
+        <v>0.5876945415063286</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.142017875824155</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292234620838689</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.113766003591232</v>
+        <v>-5.880485910076866</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.512776779366737</v>
+        <v>0.6060888167724836</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.142017875824155</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.273428879622485</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.873335506786372</v>
+        <v>-5.640055413272005</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6106920547135584</v>
+        <v>0.7040040921193054</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.901587379019295</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.419430254330278</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.801092938615177</v>
+        <v>-5.567812845100811</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6435183958168564</v>
+        <v>0.7368304332226034</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.901587379019295</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.423359568165098</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.748094616333789</v>
+        <v>-5.514814522819423</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6653963086467516</v>
+        <v>0.7587083460524986</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8462511200173561</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457239907483602</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.639289730854062</v>
+        <v>-5.406009637339696</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7059163340586361</v>
+        <v>0.7992283714643826</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8462511200173561</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454237978703595</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.419268932817052</v>
+        <v>-5.185988839302685</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7955036902840544</v>
+        <v>0.888815727689801</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7050312749493759</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.540548922754997</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.286401243753774</v>
+        <v>-5.053121150239408</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8645449487111887</v>
+        <v>0.9578569861169353</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7050312749493759</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.55644310555682</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.126886140234404</v>
+        <v>-4.893606046720038</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9294968345592385</v>
+        <v>1.022808871964985</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.545516171430006</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.653298012108745</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.982213995134667</v>
+        <v>-4.7489339016203</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9974537951605735</v>
+        <v>1.09076583256632</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4008440263302686</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750189401730027</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.042088822492359</v>
+        <v>-4.808808728977993</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9595413556189225</v>
+        <v>1.052853393024669</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4607188536879607</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.700301996716837</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.95528932471335</v>
+        <v>-4.722009231198983</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.016661648053092</v>
+        <v>1.109973685458839</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4607188536879607</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.722702490039403</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.957759031175156</v>
+        <v>-4.724478937660789</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.015746166841782</v>
+        <v>1.109058204247529</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4631885601497668</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.721293067535732</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.026129217499166</v>
+        <v>-4.7928491239848</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9994050147868796</v>
+        <v>1.092717052192626</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4539128611135519</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.737865409432163</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.1346673984153</v>
+        <v>-4.901387304900934</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9464264510523175</v>
+        <v>1.039738488458064</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4539128611135519</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.728302118064054</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.165660557744006</v>
+        <v>-4.932380464229639</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7587387523612223</v>
+        <v>0.8520507897669689</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4539128611135519</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553011683104441</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.990186297951537</v>
+        <v>-4.75690620443717</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8334956882699975</v>
+        <v>0.9268077256757441</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4539128611135519</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.557578915096228</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.101122550592786</v>
+        <v>-4.867842457078419</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7648632159747049</v>
+        <v>0.8581752533804516</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4539128611135519</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.533320943857436</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.304149128136019</v>
+        <v>-5.070869034621652</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6867839701773173</v>
+        <v>0.7800960075830639</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6569394386567853</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.414636382551401</v>
+        <v>2.415393549788432</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.146223529200726</v>
+        <v>-4.912943435686359</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7601265961835666</v>
+        <v>0.8534386335893134</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6569394386567853</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.424808768983534</v>
+        <v>2.425565936220564</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.059980066174348</v>
+        <v>-4.826699972659982</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7895702519679784</v>
+        <v>0.8828822893737249</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6569394386567853</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.419755039557394</v>
+        <v>2.420512206794424</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.105286885573328</v>
+        <v>-4.872006792058961</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7632232996529118</v>
+        <v>0.8565353370586584</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6977496016660161</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387044717196381</v>
+        <v>2.387801884433411</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.134319990275629</v>
+        <v>-4.901039896761263</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7521619308050931</v>
+        <v>0.8454739682108396</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6977496016660161</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.387596590229482</v>
+        <v>2.388353757466513</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.041509508824769</v>
+        <v>-4.808229415310403</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7185588152768023</v>
+        <v>0.8118708526825491</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6049391202151567</v>
+        <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.372555570991364</v>
+        <v>2.373312738228394</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.085898978154197</v>
+        <v>-4.85261888463983</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7026765034696321</v>
+        <v>0.7959885408753788</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6493285895445844</v>
+        <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.347795365318308</v>
+        <v>2.348552532555338</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.973227759917947</v>
+        <v>-4.73994766640358</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7428206992758553</v>
+        <v>0.836132736681602</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5366573713083342</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.410473804771781</v>
+        <v>2.411230972008811</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.860850758735274</v>
+        <v>-4.627570665220907</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7932627955795917</v>
+        <v>0.8865748329853385</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5366573713083342</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.415965100602449</v>
+        <v>2.416722267839479</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.059085327622005</v>
+        <v>-4.825805234107638</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7254661697934384</v>
+        <v>0.8187782071991851</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7348919401950649</v>
+        <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.308521561038949</v>
+        <v>2.309278728275979</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.142086608647284</v>
+        <v>-4.908806515132917</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5306213773839801</v>
+        <v>0.6239334147897269</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7534628247222386</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.135734750323298</v>
+        <v>2.136491917560329</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.269153614954272</v>
+        <v>-5.035873521439905</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5999442355803906</v>
+        <v>0.6932562729861371</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7534628247222386</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.255884411042504</v>
+        <v>2.256641578279534</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.355752197935375</v>
+        <v>-5.122472104421008</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5798178284902722</v>
+        <v>0.6731298658960192</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7534628247222386</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.270397437144827</v>
+        <v>2.271154604381857</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.317368535377224</v>
+        <v>-5.084088441862857</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5925907348559014</v>
+        <v>0.685902772261648</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7150791621640874</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.290847076022086</v>
+        <v>2.291604243259116</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.140252205342057</v>
+        <v>-4.906972111827691</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6601662957152699</v>
+        <v>0.7534783331210164</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7150791621640874</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.287576104867388</v>
+        <v>2.288333272104418</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.110550081365764</v>
+        <v>-4.877269987851397</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6727305370677006</v>
+        <v>0.7660425744734471</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7195492873794007</v>
+        <v>-0.7182873419843501</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.285577421500113</v>
+        <v>2.286334588737144</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.931174660126996</v>
+        <v>-4.697894566612629</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7382676808696218</v>
+        <v>0.8315797182753686</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.562772529208682</v>
+        <v>-0.5615105838136314</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.373430451708959</v>
+        <v>2.374187618945989</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.976188873647603</v>
+        <v>-4.742908780133236</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7010694507929689</v>
+        <v>0.7943814881987157</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.5931214245232866</v>
+        <v>-0.591859479128236</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.336028569851786</v>
+        <v>2.336785737088816</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.243193383920038</v>
+        <v>-5.009913290405671</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5999592090229409</v>
+        <v>0.6932712464286874</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7874844625662352</v>
+        <v>-0.7862225171711845</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.225102309364962</v>
+        <v>2.225859476601993</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.34439116535721</v>
+        <v>-5.111111071842844</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5586840183445729</v>
+        <v>0.6519960557503195</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.8558932761115543</v>
+        <v>-0.8546313307165037</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.183260943134272</v>
+        <v>2.184018110371303</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.311915579186438</v>
+        <v>-5.078635485672072</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5692742143671987</v>
+        <v>0.6625862517729453</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.8558932761115543</v>
+        <v>-0.8546313307165037</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.180860904688589</v>
+        <v>2.18161807192562</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.292877451479141</v>
+        <v>-5.059597357964774</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5734141846583625</v>
+        <v>0.666726222064109</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9140768874427488</v>
+        <v>-0.9128149420476982</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.142475457098117</v>
+        <v>2.143232624335147</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.324004082629759</v>
+        <v>-5.090723989115393</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7385454011367956</v>
+        <v>0.8318574385425421</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9140768874427488</v>
+        <v>-0.9128149420476982</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.320057326036798</v>
+        <v>2.320814493273828</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.376324463230551</v>
+        <v>-5.143044369716185</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7184505778826127</v>
+        <v>0.8117626152883592</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.8791300274338767</v>
+        <v>-0.877868082038826</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.341858771028255</v>
+        <v>2.342615938265285</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.52064736915547</v>
+        <v>-5.166251479195172</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6667299459095708</v>
+        <v>0.8084883018936901</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.8791300274338767</v>
+        <v>-0.877868082038826</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.347867301425181</v>
+        <v>2.348624468662211</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.372904398920467</v>
+        <v>-5.01850850896017</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8049797817955939</v>
+        <v>0.9467381377797128</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7113226701989935</v>
+        <v>-0.7100607248039429</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.527704363558132</v>
+        <v>2.528461530795163</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.474919081451689</v>
+        <v>-5.120523191491391</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7669675303145862</v>
+        <v>0.9087258862987055</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7113226701989935</v>
+        <v>-0.7100607248039429</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.530497985089613</v>
+        <v>2.531255152326644</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.338309737357596</v>
+        <v>-4.983913847397298</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8222736163438817</v>
+        <v>0.9640319723280009</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5747133261049011</v>
+        <v>-0.5734513807098505</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.613125939937727</v>
+        <v>2.613883107174757</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.481075070180246</v>
+        <v>-5.126679180219949</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7642479599549321</v>
+        <v>0.906006315939051</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7174786589275515</v>
+        <v>-0.7162167135325008</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.526547216984247</v>
+        <v>2.527304384221277</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.418777071404124</v>
+        <v>-5.064381181443826</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8555027132622017</v>
+        <v>0.9972610692463206</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7174786589275515</v>
+        <v>-0.7162167135325008</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.592882770781068</v>
+        <v>2.593639938018098</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.216986873738966</v>
+        <v>-4.862590983778668</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.644799664717663</v>
+        <v>0.7865580207017819</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5194604667583971</v>
+        <v>-0.5181985213633464</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.420274558471959</v>
+        <v>2.421031725708989</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.157096192096373</v>
+        <v>-4.802700302136075</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7390461696968753</v>
+        <v>0.8808045256809947</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.4595697851158036</v>
+        <v>-0.458307839720753</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.52649919977969</v>
+        <v>2.527256367016721</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.254836736721347</v>
+        <v>-4.900440846761049</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7145776879629295</v>
+        <v>0.8563360439470484</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4754590632487838</v>
+        <v>-0.4741971178537331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.531593369015946</v>
+        <v>2.532350536252976</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.431174496844276</v>
+        <v>-5.076778606883979</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6425785647384292</v>
+        <v>0.7843369207225486</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.6517968233717132</v>
+        <v>-0.6505348779766625</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.42432669376686</v>
+        <v>2.42508386100389</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.430485124683053</v>
+        <v>-5.076089234722756</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6413459316428471</v>
+        <v>0.783104287626966</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.6517968233717132</v>
+        <v>-0.6505348779766625</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.422818311806788</v>
+        <v>2.423575479043818</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.437056089737646</v>
+        <v>-5.082660199777348</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6385804130564461</v>
+        <v>0.7803387690405654</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.6583677884263062</v>
+        <v>-0.6571058430312555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.418738600209469</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.429102119442874</v>
+        <v>-5.074706229482576</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6417620011743552</v>
+        <v>0.7835203571584741</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.6583677884263062</v>
+        <v>-0.6571058430312555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.418738600209469</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.418728743109787</v>
+        <v>-5.064332853149489</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6522931087353947</v>
+        <v>0.7940514647195136</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6479944120932188</v>
+        <v>-0.6467324666981682</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.431344383037126</v>
+        <v>2.432101550274156</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.29104443331549</v>
+        <v>-4.936648543355193</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7082592060278379</v>
+        <v>0.850017562011957</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5203101022989224</v>
+        <v>-0.5190481569038717</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.512847342288429</v>
+        <v>2.513604509525459</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.351711023717879</v>
+        <v>-4.997315133757581</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6707472423427547</v>
+        <v>0.8125055983268736</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6020084190174561</v>
+        <v>-0.6007464736224054</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.45058302473318</v>
+        <v>2.451340191970211</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.286717163784234</v>
+        <v>-4.932321273823936</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7008424889268414</v>
+        <v>0.8426008449109605</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.5751778044133007</v>
+        <v>-0.57391585901825</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.470779096106302</v>
+        <v>2.471536263343332</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.387475799541232</v>
+        <v>-5.033079909580934</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6646999742551203</v>
+        <v>0.8064583302392392</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6640033731403061</v>
+        <v>-0.6627414277452555</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.421644694501177</v>
+        <v>2.422401861738207</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.343272962455331</v>
+        <v>-4.988877072495034</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6882607116173176</v>
+        <v>0.8300190676014365</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6198005360544057</v>
+        <v>-0.618538590659355</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.454045999280554</v>
+        <v>2.454803166517585</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.380251990118774</v>
+        <v>-5.025856100158476</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.671879101021188</v>
+        <v>0.8136374570053069</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5828266342630751</v>
+        <v>-0.5815646888680245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.4746403408246</v>
+        <v>2.475397508061631</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.415031657143786</v>
+        <v>3.868729939439259</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.535590206071816</v>
+        <v>2.821991658512149</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.380251990118774</v>
+        <v>-5.129129355229357</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.671879101021188</v>
+        <v>0.7699834921066588</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.5828266342630751</v>
+        <v>-0.6848379439389051</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.528654003058184</v>
+        <v>2.411088892148806</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240604.xlsx
+++ b/tame_output/ON/bt/strategyON_20240604.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-674.5%</t>
+          <t>-674.2%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-162.3%</t>
+          <t>-162.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-299.2%</t>
+          <t>-299.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.7%</t>
+          <t>-156.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-292.5%</t>
+          <t>-282.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-204.9%</t>
+          <t>-198.7%</t>
         </is>
       </c>
     </row>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987904</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.166251479195172</v>
+        <v>-5.163301668245142</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8084883018936901</v>
+        <v>0.8096682262737018</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.877868082038826</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.01850850896017</v>
+        <v>-5.01555869801014</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9467381377797128</v>
+        <v>0.947918062159725</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7100607248039429</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.120523191491391</v>
+        <v>-5.117573380541361</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9087258862987055</v>
+        <v>0.9099058106787172</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7100607248039429</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.983913847397298</v>
+        <v>-4.980964036447268</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9640319723280009</v>
+        <v>0.9652118967080128</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.5734513807098505</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.126679180219949</v>
+        <v>-5.123729369269919</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.906006315939051</v>
+        <v>0.9071862403190631</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7162167135325008</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.064381181443826</v>
+        <v>-5.061431370493796</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9972610692463206</v>
+        <v>0.9984409936263328</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7162167135325008</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.862590983778668</v>
+        <v>-4.859641172828638</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7865580207017819</v>
+        <v>0.7877379450817941</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.5181985213633464</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.802700302136075</v>
+        <v>-4.799750491186045</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8808045256809947</v>
+        <v>0.8819844500610066</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.458307839720753</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.900440846761049</v>
+        <v>-4.89749103581102</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8563360439470484</v>
+        <v>0.8575159683270603</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.4741971178537331</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.076778606883979</v>
+        <v>-5.073828795933949</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7843369207225486</v>
+        <v>0.7855168451025603</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.6505348779766625</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.076089234722756</v>
+        <v>-5.073139423772726</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.783104287626966</v>
+        <v>0.7842842120069782</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.6505348779766625</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.082660199777348</v>
+        <v>-5.079710388827318</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7803387690405654</v>
+        <v>0.7815186934205771</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.6571058430312555</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.074706229482576</v>
+        <v>-5.071756418532546</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7835203571584741</v>
+        <v>0.7847002815384863</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.6571058430312555</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.064332853149489</v>
+        <v>-5.061383042199459</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7940514647195136</v>
+        <v>0.7952313890995257</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.6467324666981682</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.936648543355193</v>
+        <v>-4.933698732405163</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.850017562011957</v>
+        <v>0.8511974863919689</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5190481569038717</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.997315133757581</v>
+        <v>-4.994365322807552</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8125055983268736</v>
+        <v>0.8136855227068858</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.6007464736224054</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.932321273823936</v>
+        <v>-4.929371462873906</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8426008449109605</v>
+        <v>0.8437807692909725</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.57391585901825</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.033079909580934</v>
+        <v>-5.030130098630904</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8064583302392392</v>
+        <v>0.8076382546192513</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.6627414277452555</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.988877072495034</v>
+        <v>-4.985927261545004</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8300190676014365</v>
+        <v>0.8311989919814486</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.618538590659355</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.025856100158476</v>
+        <v>-5.022906289208446</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8136374570053069</v>
+        <v>0.814817381385319</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.5815646888680245</v>
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.868729939439259</v>
+        <v>3.868729939439257</v>
       </c>
       <c r="C1985" t="n">
         <v>2.821991658512149</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.129129355229357</v>
+        <v>-5.126444370715158</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7699834921066588</v>
+        <v>0.7710574859123382</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6848379439389051</v>
+        <v>-0.5815646888680245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.411088892148806</v>
+        <v>2.473052845191335</v>
       </c>
     </row>
   </sheetData>
